--- a/ML/Data/MLPARTA.xlsx
+++ b/ML/Data/MLPARTA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Jonathan/School/Python/MECH390/ML/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97382C68-FA6E-9D4E-9315-59024936806B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3F466A-83F8-D14C-9ECD-E6DC10FEB56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{BC048AF6-1244-4540-8538-620CC49C9B23}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{BC048AF6-1244-4540-8538-620CC49C9B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Geometry" sheetId="2" r:id="rId1"/>
@@ -135,7 +135,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -547,7 +547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19614FDF-CE64-4048-A8B4-7032B403BE32}">
   <dimension ref="A1:AC111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
@@ -568,7 +568,7 @@
     <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:29" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -655,7 +655,7 @@
       </c>
       <c r="AC1" s="3"/>
     </row>
-    <row r="2" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="2" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
         <v>110</v>
       </c>
@@ -754,15 +754,15 @@
         <v>64.356699824191494</v>
       </c>
       <c r="AA2" s="10">
-        <f t="shared" ref="AA2:AA33" si="7">ASIN($F2/$D2)</f>
+        <f>ASIN($F2/$D2)</f>
         <v>0.32702813658891794</v>
       </c>
       <c r="AB2" s="2">
-        <f t="shared" ref="AB2:AB33" si="8">(PI()+2*$AA2)/(PI()-2*$AA2)</f>
+        <f>(PI()+2*$AA2)/(PI()-2*$AA2)</f>
         <v>1.5258666995411085</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="3" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>110</v>
       </c>
@@ -770,7 +770,7 @@
         <v>2700</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ref="C3:C66" si="9">(2*PI()*30/60)</f>
+        <f t="shared" ref="C3:C66" si="7">(2*PI()*30/60)</f>
         <v>3.1415926535897927</v>
       </c>
       <c r="D3" s="4">
@@ -789,23 +789,23 @@
         <v>1.1692995882295725</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I66" si="10">$G3*$D3*$B3</f>
+        <f t="shared" ref="I3:I66" si="8">$G3*$D3*$B3</f>
         <v>0.13684244328482659</v>
       </c>
       <c r="J3" s="5">
-        <f t="shared" ref="J3:J66" si="11">$E3*$G3*$B3</f>
+        <f t="shared" ref="J3:J66" si="9">$E3*$G3*$B3</f>
         <v>0.81756678904826396</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K66" si="12">$I3+$J3</f>
+        <f t="shared" ref="K3:K66" si="10">$I3+$J3</f>
         <v>0.95440923233309061</v>
       </c>
       <c r="L3" s="5">
-        <f t="shared" ref="L3:L66" si="13">0.2*$K3</f>
+        <f t="shared" ref="L3:L66" si="11">0.2*$K3</f>
         <v>0.19088184646661813</v>
       </c>
       <c r="M3" s="8">
-        <f t="shared" ref="M3:M66" si="14">$D3*SIN($H3)+SQRT($E3^2-($D3*COS($H3)-$F3^2))</f>
+        <f t="shared" ref="M3:M66" si="12">$D3*SIN($H3)+SQRT($E3^2-($D3*COS($H3)-$F3^2))</f>
         <v>0.78161151566879439</v>
       </c>
       <c r="N3" s="8">
@@ -821,15 +821,15 @@
         <v>-0.98121117719007911</v>
       </c>
       <c r="Q3" s="2">
-        <f t="shared" ref="Q3:Q66" si="15">$T3*COS($N3)</f>
+        <f t="shared" ref="Q3:Q66" si="13">$T3*COS($N3)</f>
         <v>109.81270459872427</v>
       </c>
       <c r="R3" s="9">
-        <f t="shared" ref="R3:R66" si="16">$L3*$P3</f>
+        <f t="shared" ref="R3:R66" si="14">$L3*$P3</f>
         <v>-0.1872954012757263</v>
       </c>
       <c r="S3" s="9">
-        <f t="shared" ref="S3:S66" si="17">$Q3+$R3</f>
+        <f t="shared" ref="S3:S66" si="15">$Q3+$R3</f>
         <v>109.62540919744853</v>
       </c>
       <c r="T3" s="9">
@@ -861,15 +861,15 @@
         <v>49.425066763882874</v>
       </c>
       <c r="AA3" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AA2:AA33" si="16">ASIN($F3/$D3)</f>
         <v>1.0428571329427976</v>
       </c>
       <c r="AB3" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="AB2:AB33" si="17">(PI()+2*$AA3)/(PI()-2*$AA3)</f>
         <v>4.9506713844585359</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="4" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>110</v>
       </c>
@@ -877,7 +877,7 @@
         <v>2700</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D4" s="4">
@@ -896,23 +896,23 @@
         <v>0.32833879550866041</v>
       </c>
       <c r="I4" s="5">
+        <f t="shared" si="8"/>
+        <v>0.18783079798827679</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="9"/>
+        <v>0.84150240524194575</v>
+      </c>
+      <c r="K4" s="5">
         <f t="shared" si="10"/>
-        <v>0.18783079798827679</v>
-      </c>
-      <c r="J4" s="5">
+        <v>1.0293332032302225</v>
+      </c>
+      <c r="L4" s="5">
         <f t="shared" si="11"/>
-        <v>0.84150240524194575</v>
-      </c>
-      <c r="K4" s="5">
+        <v>0.20586664064604451</v>
+      </c>
+      <c r="M4" s="8">
         <f t="shared" si="12"/>
-        <v>1.0293332032302225</v>
-      </c>
-      <c r="L4" s="5">
-        <f t="shared" si="13"/>
-        <v>0.20586664064604451</v>
-      </c>
-      <c r="M4" s="8">
-        <f t="shared" si="14"/>
         <v>0.56109656088480953</v>
       </c>
       <c r="N4" s="8">
@@ -928,15 +928,15 @@
         <v>-0.80742762541073976</v>
       </c>
       <c r="Q4" s="2">
+        <f t="shared" si="13"/>
+        <v>109.83377758719188</v>
+      </c>
+      <c r="R4" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.16622241280812181</v>
+      </c>
+      <c r="S4" s="9">
         <f t="shared" si="15"/>
-        <v>109.83377758719188</v>
-      </c>
-      <c r="R4" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.16622241280812181</v>
-      </c>
-      <c r="S4" s="9">
-        <f t="shared" si="17"/>
         <v>109.66755517438375</v>
       </c>
       <c r="T4" s="9">
@@ -968,15 +968,15 @@
         <v>41.65006934003484</v>
       </c>
       <c r="AA4" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.37029092194945273</v>
       </c>
       <c r="AB4" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>1.6168917198621442</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="5" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>110</v>
       </c>
@@ -984,7 +984,7 @@
         <v>2700</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D5" s="4">
@@ -1003,23 +1003,23 @@
         <v>1.0370788389756866</v>
       </c>
       <c r="I5" s="5">
+        <f t="shared" si="8"/>
+        <v>8.6493869772345466E-2</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="9"/>
+        <v>0.43482136214941597</v>
+      </c>
+      <c r="K5" s="5">
         <f t="shared" si="10"/>
-        <v>8.6493869772345466E-2</v>
-      </c>
-      <c r="J5" s="5">
+        <v>0.52131523192176143</v>
+      </c>
+      <c r="L5" s="5">
         <f t="shared" si="11"/>
-        <v>0.43482136214941597</v>
-      </c>
-      <c r="K5" s="5">
+        <v>0.1042630463843523</v>
+      </c>
+      <c r="M5" s="8">
         <f t="shared" si="12"/>
-        <v>0.52131523192176143</v>
-      </c>
-      <c r="L5" s="5">
-        <f t="shared" si="13"/>
-        <v>0.1042630463843523</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" si="14"/>
         <v>0.87943910191207397</v>
       </c>
       <c r="N5" s="8">
@@ -1035,15 +1035,15 @@
         <v>-1.2630514119812917</v>
       </c>
       <c r="Q5" s="2">
+        <f t="shared" si="13"/>
+        <v>109.86831041204675</v>
+      </c>
+      <c r="R5" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13168958795322708</v>
+      </c>
+      <c r="S5" s="9">
         <f t="shared" si="15"/>
-        <v>109.86831041204675</v>
-      </c>
-      <c r="R5" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13168958795322708</v>
-      </c>
-      <c r="S5" s="9">
-        <f t="shared" si="17"/>
         <v>109.73662082409352</v>
       </c>
       <c r="T5" s="9">
@@ -1075,15 +1075,15 @@
         <v>69.763523110885671</v>
       </c>
       <c r="AA5" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.59944496284669868</v>
       </c>
       <c r="AB5" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.2342494901333496</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="6" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>110</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>2700</v>
       </c>
       <c r="C6" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D6" s="4">
@@ -1110,23 +1110,23 @@
         <v>1.74511524240975</v>
       </c>
       <c r="I6" s="5">
+        <f t="shared" si="8"/>
+        <v>1.6823760713083506E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="9"/>
+        <v>0.17917753401964698</v>
+      </c>
+      <c r="K6" s="5">
         <f t="shared" si="10"/>
-        <v>1.6823760713083506E-2</v>
-      </c>
-      <c r="J6" s="5">
+        <v>0.19600129473273048</v>
+      </c>
+      <c r="L6" s="5">
         <f t="shared" si="11"/>
-        <v>0.17917753401964698</v>
-      </c>
-      <c r="K6" s="5">
+        <v>3.92002589465461E-2</v>
+      </c>
+      <c r="M6" s="8">
         <f t="shared" si="12"/>
-        <v>0.19600129473273048</v>
-      </c>
-      <c r="L6" s="5">
-        <f t="shared" si="13"/>
-        <v>3.92002589465461E-2</v>
-      </c>
-      <c r="M6" s="8">
-        <f t="shared" si="14"/>
         <v>0.68883147445567039</v>
       </c>
       <c r="N6" s="8">
@@ -1142,15 +1142,15 @@
         <v>-0.50692755034308601</v>
       </c>
       <c r="Q6" s="2">
+        <f t="shared" si="13"/>
+        <v>109.98012830875943</v>
+      </c>
+      <c r="R6" s="9">
+        <f t="shared" si="14"/>
+        <v>-1.9871691240587255E-2</v>
+      </c>
+      <c r="S6" s="9">
         <f t="shared" si="15"/>
-        <v>109.98012830875943</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="16"/>
-        <v>-1.9871691240587255E-2</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="17"/>
         <v>109.96025661751885</v>
       </c>
       <c r="T6" s="9">
@@ -1182,15 +1182,15 @@
         <v>17.453515356084203</v>
       </c>
       <c r="AA6" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.1287615947464511</v>
       </c>
       <c r="AB6" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>6.1071172145936385</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="7" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>110</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>2700</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D7" s="4">
@@ -1217,23 +1217,23 @@
         <v>0.41474937456770677</v>
       </c>
       <c r="I7" s="5">
+        <f t="shared" si="8"/>
+        <v>0.13900777833216152</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="9"/>
+        <v>0.62180353133252475</v>
+      </c>
+      <c r="K7" s="5">
         <f t="shared" si="10"/>
-        <v>0.13900777833216152</v>
-      </c>
-      <c r="J7" s="5">
+        <v>0.76081130966468624</v>
+      </c>
+      <c r="L7" s="5">
         <f t="shared" si="11"/>
-        <v>0.62180353133252475</v>
-      </c>
-      <c r="K7" s="5">
+        <v>0.15216226193293725</v>
+      </c>
+      <c r="M7" s="8">
         <f t="shared" si="12"/>
-        <v>0.76081130966468624</v>
-      </c>
-      <c r="L7" s="5">
-        <f t="shared" si="13"/>
-        <v>0.15216226193293725</v>
-      </c>
-      <c r="M7" s="8">
-        <f t="shared" si="14"/>
         <v>0.54350798334168471</v>
       </c>
       <c r="N7" s="8">
@@ -1249,15 +1249,15 @@
         <v>-0.95418489613637802</v>
       </c>
       <c r="Q7" s="2">
+        <f t="shared" si="13"/>
+        <v>109.85480906790166</v>
+      </c>
+      <c r="R7" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.14519093209835607</v>
+      </c>
+      <c r="S7" s="9">
         <f t="shared" si="15"/>
-        <v>109.85480906790166</v>
-      </c>
-      <c r="R7" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.14519093209835607</v>
-      </c>
-      <c r="S7" s="9">
-        <f t="shared" si="17"/>
         <v>109.7096181358033</v>
       </c>
       <c r="T7" s="9">
@@ -1289,15 +1289,15 @@
         <v>43.453626459489769</v>
       </c>
       <c r="AA7" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.0028917331760414</v>
       </c>
       <c r="AB7" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>4.5319021696419828</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="8" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>110</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>2700</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D8" s="4">
@@ -1324,23 +1324,23 @@
         <v>1.9313631904507058</v>
       </c>
       <c r="I8" s="5">
+        <f t="shared" si="8"/>
+        <v>6.8564971179113463E-2</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="9"/>
+        <v>0.24000315734832908</v>
+      </c>
+      <c r="K8" s="5">
         <f t="shared" si="10"/>
-        <v>6.8564971179113463E-2</v>
-      </c>
-      <c r="J8" s="5">
+        <v>0.30856812852744253</v>
+      </c>
+      <c r="L8" s="5">
         <f t="shared" si="11"/>
-        <v>0.24000315734832908</v>
-      </c>
-      <c r="K8" s="5">
+        <v>6.1713625705488509E-2</v>
+      </c>
+      <c r="M8" s="8">
         <f t="shared" si="12"/>
-        <v>0.30856812852744253</v>
-      </c>
-      <c r="L8" s="5">
-        <f t="shared" si="13"/>
-        <v>6.1713625705488509E-2</v>
-      </c>
-      <c r="M8" s="8">
-        <f t="shared" si="14"/>
         <v>0.84330378678340834</v>
       </c>
       <c r="N8" s="8">
@@ -1356,15 +1356,15 @@
         <v>-1.1997785331083184</v>
       </c>
       <c r="Q8" s="2">
+        <f t="shared" si="13"/>
+        <v>109.92595731667828</v>
+      </c>
+      <c r="R8" s="9">
+        <f t="shared" si="14"/>
+        <v>-7.404268332172681E-2</v>
+      </c>
+      <c r="S8" s="9">
         <f t="shared" si="15"/>
-        <v>109.92595731667828</v>
-      </c>
-      <c r="R8" s="9">
-        <f t="shared" si="16"/>
-        <v>-7.404268332172681E-2</v>
-      </c>
-      <c r="S8" s="9">
-        <f t="shared" si="17"/>
         <v>109.85191463335656</v>
       </c>
       <c r="T8" s="9">
@@ -1396,15 +1396,15 @@
         <v>41.415726299654253</v>
       </c>
       <c r="AA8" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.4022764782217389</v>
       </c>
       <c r="AB8" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>1.6885231409854886</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="9" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>110</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>2700</v>
       </c>
       <c r="C9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D9" s="4">
@@ -1431,23 +1431,23 @@
         <v>6.2276450838906969E-2</v>
       </c>
       <c r="I9" s="5">
+        <f t="shared" si="8"/>
+        <v>8.4530143803866475E-2</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="9"/>
+        <v>0.40615254908517162</v>
+      </c>
+      <c r="K9" s="5">
         <f t="shared" si="10"/>
-        <v>8.4530143803866475E-2</v>
-      </c>
-      <c r="J9" s="5">
+        <v>0.4906826928890381</v>
+      </c>
+      <c r="L9" s="5">
         <f t="shared" si="11"/>
-        <v>0.40615254908517162</v>
-      </c>
-      <c r="K9" s="5">
+        <v>9.813653857780763E-2</v>
+      </c>
+      <c r="M9" s="8">
         <f t="shared" si="12"/>
-        <v>0.4906826928890381</v>
-      </c>
-      <c r="L9" s="5">
-        <f t="shared" si="13"/>
-        <v>9.813653857780763E-2</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" si="14"/>
         <v>0.56754084441602137</v>
       </c>
       <c r="N9" s="8">
@@ -1463,15 +1463,15 @@
         <v>-0.63095062585073769</v>
       </c>
       <c r="Q9" s="2">
+        <f t="shared" si="13"/>
+        <v>109.93808068956551</v>
+      </c>
+      <c r="R9" s="9">
+        <f t="shared" si="14"/>
+        <v>-6.1919310434492787E-2</v>
+      </c>
+      <c r="S9" s="9">
         <f t="shared" si="15"/>
-        <v>109.93808068956551</v>
-      </c>
-      <c r="R9" s="9">
-        <f t="shared" si="16"/>
-        <v>-6.1919310434492787E-2</v>
-      </c>
-      <c r="S9" s="9">
-        <f t="shared" si="17"/>
         <v>109.87616137913102</v>
       </c>
       <c r="T9" s="9">
@@ -1503,15 +1503,15 @@
         <v>34.730404952379033</v>
       </c>
       <c r="AA9" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.93034522998139235</v>
       </c>
       <c r="AB9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>3.9052810889394216</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="10" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>110</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>2700</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D10" s="4">
@@ -1538,23 +1538,23 @@
         <v>0.17589678112930671</v>
       </c>
       <c r="I10" s="5">
+        <f t="shared" si="8"/>
+        <v>0.10374494164665489</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="9"/>
+        <v>0.47203930322920251</v>
+      </c>
+      <c r="K10" s="5">
         <f t="shared" si="10"/>
-        <v>0.10374494164665489</v>
-      </c>
-      <c r="J10" s="5">
+        <v>0.57578424487585744</v>
+      </c>
+      <c r="L10" s="5">
         <f t="shared" si="11"/>
-        <v>0.47203930322920251</v>
-      </c>
-      <c r="K10" s="5">
+        <v>0.11515684897517149</v>
+      </c>
+      <c r="M10" s="8">
         <f t="shared" si="12"/>
-        <v>0.57578424487585744</v>
-      </c>
-      <c r="L10" s="5">
-        <f t="shared" si="13"/>
-        <v>0.11515684897517149</v>
-      </c>
-      <c r="M10" s="8">
-        <f t="shared" si="14"/>
         <v>0.26530928686462835</v>
       </c>
       <c r="N10" s="8">
@@ -1570,15 +1570,15 @@
         <v>-0.44113220172899315</v>
       </c>
       <c r="Q10" s="2">
+        <f t="shared" si="13"/>
+        <v>109.94920060566741</v>
+      </c>
+      <c r="R10" s="9">
+        <f t="shared" si="14"/>
+        <v>-5.079939433259055E-2</v>
+      </c>
+      <c r="S10" s="9">
         <f t="shared" si="15"/>
-        <v>109.94920060566741</v>
-      </c>
-      <c r="R10" s="9">
-        <f t="shared" si="16"/>
-        <v>-5.079939433259055E-2</v>
-      </c>
-      <c r="S10" s="9">
-        <f t="shared" si="17"/>
         <v>109.89840121133483</v>
       </c>
       <c r="T10" s="9">
@@ -1610,15 +1610,15 @@
         <v>13.605454567715686</v>
       </c>
       <c r="AA10" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.74645830319411133</v>
       </c>
       <c r="AB10" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.8110490643959669</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="11" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>110</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>2700</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D11" s="4">
@@ -1645,23 +1645,23 @@
         <v>2.0395973316284159</v>
       </c>
       <c r="I11" s="5">
+        <f t="shared" si="8"/>
+        <v>4.8411393612794167E-2</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="9"/>
+        <v>0.29148604512645637</v>
+      </c>
+      <c r="K11" s="5">
         <f t="shared" si="10"/>
-        <v>4.8411393612794167E-2</v>
-      </c>
-      <c r="J11" s="5">
+        <v>0.33989743873925055</v>
+      </c>
+      <c r="L11" s="5">
         <f t="shared" si="11"/>
-        <v>0.29148604512645637</v>
-      </c>
-      <c r="K11" s="5">
+        <v>6.7979487747850106E-2</v>
+      </c>
+      <c r="M11" s="8">
         <f t="shared" si="12"/>
-        <v>0.33989743873925055</v>
-      </c>
-      <c r="L11" s="5">
-        <f t="shared" si="13"/>
-        <v>6.7979487747850106E-2</v>
-      </c>
-      <c r="M11" s="8">
-        <f t="shared" si="14"/>
         <v>0.64410816450189079</v>
       </c>
       <c r="N11" s="8">
@@ -1677,15 +1677,15 @@
         <v>-0.61787977107021075</v>
       </c>
       <c r="Q11" s="2">
+        <f t="shared" si="13"/>
+        <v>109.9579968496729</v>
+      </c>
+      <c r="R11" s="9">
+        <f t="shared" si="14"/>
+        <v>-4.200315032711182E-2</v>
+      </c>
+      <c r="S11" s="9">
         <f t="shared" si="15"/>
-        <v>109.9579968496729</v>
-      </c>
-      <c r="R11" s="9">
-        <f t="shared" si="16"/>
-        <v>-4.200315032711182E-2</v>
-      </c>
-      <c r="S11" s="9">
-        <f t="shared" si="17"/>
         <v>109.91599369934579</v>
       </c>
       <c r="T11" s="9">
@@ -1717,15 +1717,15 @@
         <v>18.012879996881974</v>
       </c>
       <c r="AA11" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.2402393103921741</v>
       </c>
       <c r="AB11" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>8.5039357741611035</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="12" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>110</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>2700</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D12" s="4">
@@ -1752,23 +1752,23 @@
         <v>1.9018788446325792</v>
       </c>
       <c r="I12" s="5">
+        <f t="shared" si="8"/>
+        <v>5.2432699279695245E-2</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="9"/>
+        <v>0.19127516812003836</v>
+      </c>
+      <c r="K12" s="5">
         <f t="shared" si="10"/>
-        <v>5.2432699279695245E-2</v>
-      </c>
-      <c r="J12" s="5">
+        <v>0.2437078673997336</v>
+      </c>
+      <c r="L12" s="5">
         <f t="shared" si="11"/>
-        <v>0.19127516812003836</v>
-      </c>
-      <c r="K12" s="5">
+        <v>4.8741573479946725E-2</v>
+      </c>
+      <c r="M12" s="8">
         <f t="shared" si="12"/>
-        <v>0.2437078673997336</v>
-      </c>
-      <c r="L12" s="5">
-        <f t="shared" si="13"/>
-        <v>4.8741573479946725E-2</v>
-      </c>
-      <c r="M12" s="8">
-        <f t="shared" si="14"/>
         <v>0.68307458025811596</v>
       </c>
       <c r="N12" s="8">
@@ -1784,15 +1784,15 @@
         <v>-0.86373936740007728</v>
       </c>
       <c r="Q12" s="2">
+        <f t="shared" si="13"/>
+        <v>109.95789998415634</v>
+      </c>
+      <c r="R12" s="9">
+        <f t="shared" si="14"/>
+        <v>-4.2100015843653568E-2</v>
+      </c>
+      <c r="S12" s="9">
         <f t="shared" si="15"/>
-        <v>109.95789998415634</v>
-      </c>
-      <c r="R12" s="9">
-        <f t="shared" si="16"/>
-        <v>-4.2100015843653568E-2</v>
-      </c>
-      <c r="S12" s="9">
-        <f t="shared" si="17"/>
         <v>109.91579996831268</v>
       </c>
       <c r="T12" s="9">
@@ -1824,15 +1824,15 @@
         <v>34.565684643556573</v>
       </c>
       <c r="AA12" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.92315697701683375</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>3.8508365877804893</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="13" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>110</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>2700</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D13" s="4">
@@ -1859,23 +1859,23 @@
         <v>0.1315835501232375</v>
       </c>
       <c r="I13" s="5">
+        <f t="shared" si="8"/>
+        <v>7.266639472253604E-2</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="9"/>
+        <v>0.27634349800814711</v>
+      </c>
+      <c r="K13" s="5">
         <f t="shared" si="10"/>
-        <v>7.266639472253604E-2</v>
-      </c>
-      <c r="J13" s="5">
+        <v>0.34900989273068317</v>
+      </c>
+      <c r="L13" s="5">
         <f t="shared" si="11"/>
-        <v>0.27634349800814711</v>
-      </c>
-      <c r="K13" s="5">
+        <v>6.9801978546136637E-2</v>
+      </c>
+      <c r="M13" s="8">
         <f t="shared" si="12"/>
-        <v>0.34900989273068317</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" si="13"/>
-        <v>6.9801978546136637E-2</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" si="14"/>
         <v>0.40796726890231622</v>
       </c>
       <c r="N13" s="8">
@@ -1891,15 +1891,15 @@
         <v>-0.7623921572658704</v>
       </c>
       <c r="Q13" s="2">
+        <f t="shared" si="13"/>
+        <v>109.94678351899479</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="14"/>
+        <v>-5.3216481005215116E-2</v>
+      </c>
+      <c r="S13" s="9">
         <f t="shared" si="15"/>
-        <v>109.94678351899479</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="16"/>
-        <v>-5.3216481005215116E-2</v>
-      </c>
-      <c r="S13" s="9">
-        <f t="shared" si="17"/>
         <v>109.89356703798958</v>
       </c>
       <c r="T13" s="9">
@@ -1931,15 +1931,15 @@
         <v>28.598431437196155</v>
       </c>
       <c r="AA13" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.53860498093152587</v>
       </c>
       <c r="AB13" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.0436146032226468</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="14" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>110</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>2700</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D14" s="4">
@@ -1966,23 +1966,23 @@
         <v>0.58767392028163878</v>
       </c>
       <c r="I14" s="5">
+        <f t="shared" si="8"/>
+        <v>0.13571823294489155</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="9"/>
+        <v>0.84277371289714498</v>
+      </c>
+      <c r="K14" s="5">
         <f t="shared" si="10"/>
-        <v>0.13571823294489155</v>
-      </c>
-      <c r="J14" s="5">
+        <v>0.97849194584203647</v>
+      </c>
+      <c r="L14" s="5">
         <f t="shared" si="11"/>
-        <v>0.84277371289714498</v>
-      </c>
-      <c r="K14" s="5">
+        <v>0.19569838916840732</v>
+      </c>
+      <c r="M14" s="8">
         <f t="shared" si="12"/>
-        <v>0.97849194584203647</v>
-      </c>
-      <c r="L14" s="5">
-        <f t="shared" si="13"/>
-        <v>0.19569838916840732</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" si="14"/>
         <v>0.68356854370814513</v>
       </c>
       <c r="N14" s="8">
@@ -1998,15 +1998,15 @@
         <v>-0.80773349373332082</v>
       </c>
       <c r="Q14" s="2">
+        <f t="shared" si="13"/>
+        <v>109.84192785639902</v>
+      </c>
+      <c r="R14" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.15807214360098071</v>
+      </c>
+      <c r="S14" s="9">
         <f t="shared" si="15"/>
-        <v>109.84192785639902</v>
-      </c>
-      <c r="R14" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.15807214360098071</v>
-      </c>
-      <c r="S14" s="9">
-        <f t="shared" si="17"/>
         <v>109.68385571279805</v>
       </c>
       <c r="T14" s="9">
@@ -2038,15 +2038,15 @@
         <v>44.070539260666784</v>
       </c>
       <c r="AA14" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.2234825311832571</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>8.045401286341848</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="15" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>110</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>2700</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D15" s="4">
@@ -2073,23 +2073,23 @@
         <v>1.966634565506499</v>
       </c>
       <c r="I15" s="5">
+        <f t="shared" si="8"/>
+        <v>0.1244331436114231</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="9"/>
+        <v>0.66671532926304022</v>
+      </c>
+      <c r="K15" s="5">
         <f t="shared" si="10"/>
-        <v>0.1244331436114231</v>
-      </c>
-      <c r="J15" s="5">
+        <v>0.79114847287446333</v>
+      </c>
+      <c r="L15" s="5">
         <f t="shared" si="11"/>
-        <v>0.66671532926304022</v>
-      </c>
-      <c r="K15" s="5">
+        <v>0.15822969457489267</v>
+      </c>
+      <c r="M15" s="8">
         <f t="shared" si="12"/>
-        <v>0.79114847287446333</v>
-      </c>
-      <c r="L15" s="5">
-        <f t="shared" si="13"/>
-        <v>0.15822969457489267</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" si="14"/>
         <v>0.69262649318688707</v>
       </c>
       <c r="N15" s="8">
@@ -2105,15 +2105,15 @@
         <v>-0.7292316486485696</v>
       </c>
       <c r="Q15" s="2">
+        <f t="shared" si="13"/>
+        <v>109.88461389896</v>
+      </c>
+      <c r="R15" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.11538610104000861</v>
+      </c>
+      <c r="S15" s="9">
         <f t="shared" si="15"/>
-        <v>109.88461389896</v>
-      </c>
-      <c r="R15" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.11538610104000861</v>
-      </c>
-      <c r="S15" s="9">
-        <f t="shared" si="17"/>
         <v>109.76922779792</v>
       </c>
       <c r="T15" s="9">
@@ -2145,15 +2145,15 @@
         <v>23.328742961824286</v>
       </c>
       <c r="AA15" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.3256558382497776</v>
       </c>
       <c r="AB15" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>11.815478472098958</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="2" customFormat="1" ht="14">
+    <row r="16" spans="1:29" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>110</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>2700</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D16" s="4">
@@ -2180,23 +2180,23 @@
         <v>1.0635388945498052</v>
       </c>
       <c r="I16" s="5">
+        <f t="shared" si="8"/>
+        <v>5.2847055571002298E-2</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="9"/>
+        <v>0.32379537042402268</v>
+      </c>
+      <c r="K16" s="5">
         <f t="shared" si="10"/>
-        <v>5.2847055571002298E-2</v>
-      </c>
-      <c r="J16" s="5">
+        <v>0.37664242599502495</v>
+      </c>
+      <c r="L16" s="5">
         <f t="shared" si="11"/>
-        <v>0.32379537042402268</v>
-      </c>
-      <c r="K16" s="5">
+        <v>7.5328485199004994E-2</v>
+      </c>
+      <c r="M16" s="8">
         <f t="shared" si="12"/>
-        <v>0.37664242599502495</v>
-      </c>
-      <c r="L16" s="5">
-        <f t="shared" si="13"/>
-        <v>7.5328485199004994E-2</v>
-      </c>
-      <c r="M16" s="8">
-        <f t="shared" si="14"/>
         <v>0.75999269918292656</v>
       </c>
       <c r="N16" s="8">
@@ -2212,15 +2212,15 @@
         <v>-0.93569223888433151</v>
       </c>
       <c r="Q16" s="2">
+        <f t="shared" si="13"/>
+        <v>109.92951572103237</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" si="14"/>
+        <v>-7.0484278967622216E-2</v>
+      </c>
+      <c r="S16" s="9">
         <f t="shared" si="15"/>
-        <v>109.92951572103237</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="16"/>
-        <v>-7.0484278967622216E-2</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="17"/>
         <v>109.85903144206475</v>
       </c>
       <c r="T16" s="9">
@@ -2252,15 +2252,15 @@
         <v>48.40825299167274</v>
       </c>
       <c r="AA16" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.74200994948155907</v>
       </c>
       <c r="AB16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.7905939812546627</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="17" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>110</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>2700</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D17" s="4">
@@ -2287,23 +2287,23 @@
         <v>0.32865275073488326</v>
       </c>
       <c r="I17" s="5">
+        <f t="shared" si="8"/>
+        <v>9.9450355566279472E-2</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="9"/>
+        <v>0.51256001556110975</v>
+      </c>
+      <c r="K17" s="5">
         <f t="shared" si="10"/>
-        <v>9.9450355566279472E-2</v>
-      </c>
-      <c r="J17" s="5">
+        <v>0.61201037112738921</v>
+      </c>
+      <c r="L17" s="5">
         <f t="shared" si="11"/>
-        <v>0.51256001556110975</v>
-      </c>
-      <c r="K17" s="5">
+        <v>0.12240207422547784</v>
+      </c>
+      <c r="M17" s="8">
         <f t="shared" si="12"/>
-        <v>0.61201037112738921</v>
-      </c>
-      <c r="L17" s="5">
-        <f t="shared" si="13"/>
-        <v>0.12240207422547784</v>
-      </c>
-      <c r="M17" s="8">
-        <f t="shared" si="14"/>
         <v>0.31686756288160317</v>
       </c>
       <c r="N17" s="8">
@@ -2319,15 +2319,15 @@
         <v>-0.47949186600206956</v>
       </c>
       <c r="Q17" s="2">
+        <f t="shared" si="13"/>
+        <v>109.9413092010271</v>
+      </c>
+      <c r="R17" s="9">
+        <f t="shared" si="14"/>
+        <v>-5.8690798972898195E-2</v>
+      </c>
+      <c r="S17" s="9">
         <f t="shared" si="15"/>
-        <v>109.9413092010271</v>
-      </c>
-      <c r="R17" s="9">
-        <f t="shared" si="16"/>
-        <v>-5.8690798972898195E-2</v>
-      </c>
-      <c r="S17" s="9">
-        <f t="shared" si="17"/>
         <v>109.88261840205419</v>
       </c>
       <c r="T17" s="9">
@@ -2359,15 +2359,15 @@
         <v>17.458643341796837</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.3172492067979191</v>
       </c>
       <c r="AB17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>11.390567298209676</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="18" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
         <v>110</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>2700</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D18" s="4">
@@ -2394,23 +2394,23 @@
         <v>0.1774188933580215</v>
       </c>
       <c r="I18" s="5">
+        <f t="shared" si="8"/>
+        <v>0.21865047106440438</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="9"/>
+        <v>0.8265015677485219</v>
+      </c>
+      <c r="K18" s="5">
         <f t="shared" si="10"/>
-        <v>0.21865047106440438</v>
-      </c>
-      <c r="J18" s="5">
+        <v>1.0451520388129263</v>
+      </c>
+      <c r="L18" s="5">
         <f t="shared" si="11"/>
-        <v>0.8265015677485219</v>
-      </c>
-      <c r="K18" s="5">
+        <v>0.20903040776258527</v>
+      </c>
+      <c r="M18" s="8">
         <f t="shared" si="12"/>
-        <v>1.0451520388129263</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="13"/>
-        <v>0.20903040776258527</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" si="14"/>
         <v>0.60852082299388965</v>
       </c>
       <c r="N18" s="8">
@@ -2426,15 +2426,15 @@
         <v>-1.178310477901487</v>
       </c>
       <c r="Q18" s="2">
+        <f t="shared" si="13"/>
+        <v>109.75369728033333</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.24630271966667455</v>
+      </c>
+      <c r="S18" s="9">
         <f t="shared" si="15"/>
-        <v>109.75369728033333</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.24630271966667455</v>
-      </c>
-      <c r="S18" s="9">
-        <f t="shared" si="17"/>
         <v>109.50739456066665</v>
       </c>
       <c r="T18" s="9">
@@ -2466,15 +2466,15 @@
         <v>55.750113276668763</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.71839889987277683</v>
       </c>
       <c r="AB18" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.6855961249597113</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="19" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
         <v>110</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>2700</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D19" s="4">
@@ -2501,23 +2501,23 @@
         <v>0.66276230796053737</v>
       </c>
       <c r="I19" s="5">
+        <f t="shared" si="8"/>
+        <v>0.12332603877545331</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="9"/>
+        <v>0.71666187562970862</v>
+      </c>
+      <c r="K19" s="5">
         <f t="shared" si="10"/>
-        <v>0.12332603877545331</v>
-      </c>
-      <c r="J19" s="5">
+        <v>0.83998791440516196</v>
+      </c>
+      <c r="L19" s="5">
         <f t="shared" si="11"/>
-        <v>0.71666187562970862</v>
-      </c>
-      <c r="K19" s="5">
+        <v>0.16799758288103239</v>
+      </c>
+      <c r="M19" s="8">
         <f t="shared" si="12"/>
-        <v>0.83998791440516196</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="13"/>
-        <v>0.16799758288103239</v>
-      </c>
-      <c r="M19" s="8">
-        <f t="shared" si="14"/>
         <v>0.68971901140314351</v>
       </c>
       <c r="N19" s="8">
@@ -2533,15 +2533,15 @@
         <v>-0.83165265894385298</v>
       </c>
       <c r="Q19" s="2">
+        <f t="shared" si="13"/>
+        <v>109.86028436350085</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13971563649915092</v>
+      </c>
+      <c r="S19" s="9">
         <f t="shared" si="15"/>
-        <v>109.86028436350085</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13971563649915092</v>
-      </c>
-      <c r="S19" s="9">
-        <f t="shared" si="17"/>
         <v>109.72056872700171</v>
       </c>
       <c r="T19" s="9">
@@ -2573,15 +2573,15 @@
         <v>46.568941654177529</v>
       </c>
       <c r="AA19" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.45045434263635414</v>
       </c>
       <c r="AB19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>1.8041372170385594</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="20" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
         <v>110</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>2700</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D20" s="4">
@@ -2608,23 +2608,23 @@
         <v>8.2646396588274537E-2</v>
       </c>
       <c r="I20" s="5">
+        <f t="shared" si="8"/>
+        <v>0.19974174324899596</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="9"/>
+        <v>0.68726037676580853</v>
+      </c>
+      <c r="K20" s="5">
         <f t="shared" si="10"/>
-        <v>0.19974174324899596</v>
-      </c>
-      <c r="J20" s="5">
+        <v>0.8870021200148045</v>
+      </c>
+      <c r="L20" s="5">
         <f t="shared" si="11"/>
-        <v>0.68726037676580853</v>
-      </c>
-      <c r="K20" s="5">
+        <v>0.17740042400296091</v>
+      </c>
+      <c r="M20" s="8">
         <f t="shared" si="12"/>
-        <v>0.8870021200148045</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="13"/>
-        <v>0.17740042400296091</v>
-      </c>
-      <c r="M20" s="8">
-        <f t="shared" si="14"/>
         <v>0.45449089711866431</v>
       </c>
       <c r="N20" s="8">
@@ -2640,15 +2640,15 @@
         <v>-0.90264537915442988</v>
       </c>
       <c r="Q20" s="2">
+        <f t="shared" si="13"/>
+        <v>109.83987032701368</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.16012967298630928</v>
+      </c>
+      <c r="S20" s="9">
         <f t="shared" si="15"/>
-        <v>109.83987032701368</v>
-      </c>
-      <c r="R20" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.16012967298630928</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" si="17"/>
         <v>109.67974065402737</v>
       </c>
       <c r="T20" s="9">
@@ -2680,15 +2680,15 @@
         <v>35.729047367184698</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.41264403592952753</v>
       </c>
       <c r="AB20" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>1.7125902857234792</v>
       </c>
     </row>
-    <row r="21" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="21" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
         <v>110</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>2700</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D21" s="4">
@@ -2715,23 +2715,23 @@
         <v>1.1068208479869568</v>
       </c>
       <c r="I21" s="5">
+        <f t="shared" si="8"/>
+        <v>0.10867936170782642</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="9"/>
+        <v>0.50018589705060923</v>
+      </c>
+      <c r="K21" s="5">
         <f t="shared" si="10"/>
-        <v>0.10867936170782642</v>
-      </c>
-      <c r="J21" s="5">
+        <v>0.60886525875843567</v>
+      </c>
+      <c r="L21" s="5">
         <f t="shared" si="11"/>
-        <v>0.50018589705060923</v>
-      </c>
-      <c r="K21" s="5">
+        <v>0.12177305175168714</v>
+      </c>
+      <c r="M21" s="8">
         <f t="shared" si="12"/>
-        <v>0.60886525875843567</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="13"/>
-        <v>0.12177305175168714</v>
-      </c>
-      <c r="M21" s="8">
-        <f t="shared" si="14"/>
         <v>0.65479553847104344</v>
       </c>
       <c r="N21" s="8">
@@ -2747,15 +2747,15 @@
         <v>-0.99488451712016701</v>
       </c>
       <c r="Q21" s="2">
+        <f t="shared" si="13"/>
+        <v>109.87884987620977</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.12115012379022637</v>
+      </c>
+      <c r="S21" s="9">
         <f t="shared" si="15"/>
-        <v>109.87884987620977</v>
-      </c>
-      <c r="R21" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.12115012379022637</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" si="17"/>
         <v>109.75769975241954</v>
       </c>
       <c r="T21" s="9">
@@ -2787,15 +2787,15 @@
         <v>51.302036967875431</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.49589241664753952</v>
       </c>
       <c r="AB21" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>1.9226730165667709</v>
       </c>
     </row>
-    <row r="22" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="22" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
         <v>110</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>2700</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D22" s="4">
@@ -2822,23 +2822,23 @@
         <v>1.5394443805475981</v>
       </c>
       <c r="I22" s="5">
+        <f t="shared" si="8"/>
+        <v>5.7865101125845309E-2</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="9"/>
+        <v>0.30263463462072338</v>
+      </c>
+      <c r="K22" s="5">
         <f t="shared" si="10"/>
-        <v>5.7865101125845309E-2</v>
-      </c>
-      <c r="J22" s="5">
+        <v>0.36049973574656868</v>
+      </c>
+      <c r="L22" s="5">
         <f t="shared" si="11"/>
-        <v>0.30263463462072338</v>
-      </c>
-      <c r="K22" s="5">
+        <v>7.2099947149313739E-2</v>
+      </c>
+      <c r="M22" s="8">
         <f t="shared" si="12"/>
-        <v>0.36049973574656868</v>
-      </c>
-      <c r="L22" s="5">
-        <f t="shared" si="13"/>
-        <v>7.2099947149313739E-2</v>
-      </c>
-      <c r="M22" s="8">
-        <f t="shared" si="14"/>
         <v>0.76888950918972709</v>
       </c>
       <c r="N22" s="8">
@@ -2854,15 +2854,15 @@
         <v>-0.9592217194575321</v>
       </c>
       <c r="Q22" s="2">
+        <f t="shared" si="13"/>
+        <v>109.93084016472264</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="14"/>
+        <v>-6.9159835277361914E-2</v>
+      </c>
+      <c r="S22" s="9">
         <f t="shared" si="15"/>
-        <v>109.93084016472264</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="16"/>
-        <v>-6.9159835277361914E-2</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" si="17"/>
         <v>109.86168032944528</v>
       </c>
       <c r="T22" s="9">
@@ -2894,15 +2894,15 @@
         <v>43.171117007024669</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.3504210009449336</v>
       </c>
       <c r="AB22" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>13.255646095918504</v>
       </c>
     </row>
-    <row r="23" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="23" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
         <v>110</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>2700</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D23" s="4">
@@ -2929,23 +2929,23 @@
         <v>1.5593566298725352</v>
       </c>
       <c r="I23" s="5">
+        <f t="shared" si="8"/>
+        <v>0.15261124494445966</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="9"/>
+        <v>0.40193485022654352</v>
+      </c>
+      <c r="K23" s="5">
         <f t="shared" si="10"/>
-        <v>0.15261124494445966</v>
-      </c>
-      <c r="J23" s="5">
+        <v>0.55454609517100317</v>
+      </c>
+      <c r="L23" s="5">
         <f t="shared" si="11"/>
-        <v>0.40193485022654352</v>
-      </c>
-      <c r="K23" s="5">
+        <v>0.11090921903420065</v>
+      </c>
+      <c r="M23" s="8">
         <f t="shared" si="12"/>
-        <v>0.55454609517100317</v>
-      </c>
-      <c r="L23" s="5">
-        <f t="shared" si="13"/>
-        <v>0.11090921903420065</v>
-      </c>
-      <c r="M23" s="8">
-        <f t="shared" si="14"/>
         <v>0.68365684730329024</v>
       </c>
       <c r="N23" s="8">
@@ -2961,15 +2961,15 @@
         <v>-1.1097399165067439</v>
       </c>
       <c r="Q23" s="2">
+        <f t="shared" si="13"/>
+        <v>109.87691961252916</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.12308038747084199</v>
+      </c>
+      <c r="S23" s="9">
         <f t="shared" si="15"/>
-        <v>109.87691961252916</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.12308038747084199</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" si="17"/>
         <v>109.75383922505833</v>
       </c>
       <c r="T23" s="9">
@@ -3001,15 +3001,15 @@
         <v>65.277195006844394</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.29079543585105627</v>
       </c>
       <c r="AB23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>1.4543675522547974</v>
       </c>
     </row>
-    <row r="24" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="24" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
         <v>110</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>2700</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D24" s="4">
@@ -3036,23 +3036,23 @@
         <v>0.30512494518395389</v>
       </c>
       <c r="I24" s="5">
+        <f t="shared" si="8"/>
+        <v>0.11675182206119424</v>
+      </c>
+      <c r="J24" s="5">
+        <f t="shared" si="9"/>
+        <v>0.48033392450205825</v>
+      </c>
+      <c r="K24" s="5">
         <f t="shared" si="10"/>
-        <v>0.11675182206119424</v>
-      </c>
-      <c r="J24" s="5">
+        <v>0.59708574656325253</v>
+      </c>
+      <c r="L24" s="5">
         <f t="shared" si="11"/>
-        <v>0.48033392450205825</v>
-      </c>
-      <c r="K24" s="5">
+        <v>0.11941714931265052</v>
+      </c>
+      <c r="M24" s="8">
         <f t="shared" si="12"/>
-        <v>0.59708574656325253</v>
-      </c>
-      <c r="L24" s="5">
-        <f t="shared" si="13"/>
-        <v>0.11941714931265052</v>
-      </c>
-      <c r="M24" s="8">
-        <f t="shared" si="14"/>
         <v>0.53531207768995348</v>
       </c>
       <c r="N24" s="8">
@@ -3068,15 +3068,15 @@
         <v>-1.0609178274368121</v>
       </c>
       <c r="Q24" s="2">
+        <f t="shared" si="13"/>
+        <v>109.87330821739252</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.12669178260747457</v>
+      </c>
+      <c r="S24" s="9">
         <f t="shared" si="15"/>
-        <v>109.87330821739252</v>
-      </c>
-      <c r="R24" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.12669178260747457</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" si="17"/>
         <v>109.74661643478504</v>
       </c>
       <c r="T24" s="9">
@@ -3108,15 +3108,15 @@
         <v>45.210772042590953</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.0829575296611977</v>
       </c>
       <c r="AB24" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>5.4398171528141033</v>
       </c>
     </row>
-    <row r="25" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="25" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
         <v>110</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>2700</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D25" s="4">
@@ -3143,23 +3143,23 @@
         <v>1.9393494024441849</v>
       </c>
       <c r="I25" s="5">
+        <f t="shared" si="8"/>
+        <v>7.6746375194422123E-2</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" si="9"/>
+        <v>0.34407012073196969</v>
+      </c>
+      <c r="K25" s="5">
         <f t="shared" si="10"/>
-        <v>7.6746375194422123E-2</v>
-      </c>
-      <c r="J25" s="5">
+        <v>0.42081649592639181</v>
+      </c>
+      <c r="L25" s="5">
         <f t="shared" si="11"/>
-        <v>0.34407012073196969</v>
-      </c>
-      <c r="K25" s="5">
+        <v>8.4163299185278373E-2</v>
+      </c>
+      <c r="M25" s="8">
         <f t="shared" si="12"/>
-        <v>0.42081649592639181</v>
-      </c>
-      <c r="L25" s="5">
-        <f t="shared" si="13"/>
-        <v>8.4163299185278373E-2</v>
-      </c>
-      <c r="M25" s="8">
-        <f t="shared" si="14"/>
         <v>0.56009313373726477</v>
       </c>
       <c r="N25" s="8">
@@ -3175,15 +3175,15 @@
         <v>-0.64819894123084587</v>
       </c>
       <c r="Q25" s="2">
+        <f t="shared" si="13"/>
+        <v>109.94544543857761</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="14"/>
+        <v>-5.4554561422392352E-2</v>
+      </c>
+      <c r="S25" s="9">
         <f t="shared" si="15"/>
-        <v>109.94544543857761</v>
-      </c>
-      <c r="R25" s="9">
-        <f t="shared" si="16"/>
-        <v>-5.4554561422392352E-2</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" si="17"/>
         <v>109.89089087715521</v>
       </c>
       <c r="T25" s="9">
@@ -3215,15 +3215,15 @@
         <v>24.183626161244536</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.92569335668566266</v>
       </c>
       <c r="AB25" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>3.8699088349536415</v>
       </c>
     </row>
-    <row r="26" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="26" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
         <v>110</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>2700</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D26" s="4">
@@ -3250,23 +3250,23 @@
         <v>0.94164388345029526</v>
       </c>
       <c r="I26" s="5">
+        <f t="shared" si="8"/>
+        <v>9.1183501659395857E-2</v>
+      </c>
+      <c r="J26" s="5">
+        <f t="shared" si="9"/>
+        <v>0.46405487199303858</v>
+      </c>
+      <c r="K26" s="5">
         <f t="shared" si="10"/>
-        <v>9.1183501659395857E-2</v>
-      </c>
-      <c r="J26" s="5">
+        <v>0.55523837365243445</v>
+      </c>
+      <c r="L26" s="5">
         <f t="shared" si="11"/>
-        <v>0.46405487199303858</v>
-      </c>
-      <c r="K26" s="5">
+        <v>0.11104767473048689</v>
+      </c>
+      <c r="M26" s="8">
         <f t="shared" si="12"/>
-        <v>0.55523837365243445</v>
-      </c>
-      <c r="L26" s="5">
-        <f t="shared" si="13"/>
-        <v>0.11104767473048689</v>
-      </c>
-      <c r="M26" s="8">
-        <f t="shared" si="14"/>
         <v>0.81308678918041977</v>
       </c>
       <c r="N26" s="8">
@@ -3282,15 +3282,15 @@
         <v>-1.182516979129661</v>
       </c>
       <c r="Q26" s="2">
+        <f t="shared" si="13"/>
+        <v>109.86868423913833</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13131576086166855</v>
+      </c>
+      <c r="S26" s="9">
         <f t="shared" si="15"/>
-        <v>109.86868423913833</v>
-      </c>
-      <c r="R26" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13131576086166855</v>
-      </c>
-      <c r="S26" s="9">
-        <f t="shared" si="17"/>
         <v>109.73736847827666</v>
       </c>
       <c r="T26" s="9">
@@ -3322,15 +3322,15 @@
         <v>64.677128090709573</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.74982450529140088</v>
       </c>
       <c r="AB26" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.8266753758203338</v>
       </c>
     </row>
-    <row r="27" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="27" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
         <v>110</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>2700</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D27" s="4">
@@ -3357,23 +3357,23 @@
         <v>8.0462657206234287E-2</v>
       </c>
       <c r="I27" s="5">
+        <f t="shared" si="8"/>
+        <v>4.5127793865600258E-2</v>
+      </c>
+      <c r="J27" s="5">
+        <f t="shared" si="9"/>
+        <v>0.19343239164559703</v>
+      </c>
+      <c r="K27" s="5">
         <f t="shared" si="10"/>
-        <v>4.5127793865600258E-2</v>
-      </c>
-      <c r="J27" s="5">
+        <v>0.23856018551119729</v>
+      </c>
+      <c r="L27" s="5">
         <f t="shared" si="11"/>
-        <v>0.19343239164559703</v>
-      </c>
-      <c r="K27" s="5">
+        <v>4.7712037102239459E-2</v>
+      </c>
+      <c r="M27" s="8">
         <f t="shared" si="12"/>
-        <v>0.23856018551119729</v>
-      </c>
-      <c r="L27" s="5">
-        <f t="shared" si="13"/>
-        <v>4.7712037102239459E-2</v>
-      </c>
-      <c r="M27" s="8">
-        <f t="shared" si="14"/>
         <v>0.59513541506116685</v>
       </c>
       <c r="N27" s="8">
@@ -3389,15 +3389,15 @@
         <v>-0.88551903860587555</v>
       </c>
       <c r="Q27" s="2">
+        <f t="shared" si="13"/>
+        <v>109.95775008277531</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="14"/>
+        <v>-4.2249917224702949E-2</v>
+      </c>
+      <c r="S27" s="9">
         <f t="shared" si="15"/>
-        <v>109.95775008277531</v>
-      </c>
-      <c r="R27" s="9">
-        <f t="shared" si="16"/>
-        <v>-4.2249917224702949E-2</v>
-      </c>
-      <c r="S27" s="9">
-        <f t="shared" si="17"/>
         <v>109.9155001655506</v>
       </c>
       <c r="T27" s="9">
@@ -3429,15 +3429,15 @@
         <v>44.613338821653109</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.0195378141747349</v>
       </c>
       <c r="AB27" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>4.6989462868475851</v>
       </c>
     </row>
-    <row r="28" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="28" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
         <v>110</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>2700</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D28" s="4">
@@ -3464,23 +3464,23 @@
         <v>1.226056816361498</v>
       </c>
       <c r="I28" s="5">
+        <f t="shared" si="8"/>
+        <v>8.1596167705433084E-2</v>
+      </c>
+      <c r="J28" s="5">
+        <f t="shared" si="9"/>
+        <v>0.42831743949390205</v>
+      </c>
+      <c r="K28" s="5">
         <f t="shared" si="10"/>
-        <v>8.1596167705433084E-2</v>
-      </c>
-      <c r="J28" s="5">
+        <v>0.50991360719933509</v>
+      </c>
+      <c r="L28" s="5">
         <f t="shared" si="11"/>
-        <v>0.42831743949390205</v>
-      </c>
-      <c r="K28" s="5">
+        <v>0.10198272143986703</v>
+      </c>
+      <c r="M28" s="8">
         <f t="shared" si="12"/>
-        <v>0.50991360719933509</v>
-      </c>
-      <c r="L28" s="5">
-        <f t="shared" si="13"/>
-        <v>0.10198272143986703</v>
-      </c>
-      <c r="M28" s="8">
-        <f t="shared" si="14"/>
         <v>0.83408848706211502</v>
       </c>
       <c r="N28" s="8">
@@ -3496,15 +3496,15 @@
         <v>-1.1376526523202179</v>
       </c>
       <c r="Q28" s="2">
+        <f t="shared" si="13"/>
+        <v>109.88397908646309</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.11602091353689868</v>
+      </c>
+      <c r="S28" s="9">
         <f t="shared" si="15"/>
-        <v>109.88397908646309</v>
-      </c>
-      <c r="R28" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.11602091353689868</v>
-      </c>
-      <c r="S28" s="9">
-        <f t="shared" si="17"/>
         <v>109.76795817292619</v>
       </c>
       <c r="T28" s="9">
@@ -3536,15 +3536,15 @@
         <v>58.215950932600556</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.9233987087875164</v>
       </c>
       <c r="AB28" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>3.8526478414598984</v>
       </c>
     </row>
-    <row r="29" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="29" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
         <v>110</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>2700</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D29" s="4">
@@ -3571,23 +3571,23 @@
         <v>0.90079736718606629</v>
       </c>
       <c r="I29" s="5">
+        <f t="shared" si="8"/>
+        <v>9.1822073000926901E-2</v>
+      </c>
+      <c r="J29" s="5">
+        <f t="shared" si="9"/>
+        <v>0.27868262949916239</v>
+      </c>
+      <c r="K29" s="5">
         <f t="shared" si="10"/>
-        <v>9.1822073000926901E-2</v>
-      </c>
-      <c r="J29" s="5">
+        <v>0.37050470250008927</v>
+      </c>
+      <c r="L29" s="5">
         <f t="shared" si="11"/>
-        <v>0.27868262949916239</v>
-      </c>
-      <c r="K29" s="5">
+        <v>7.4100940500017851E-2</v>
+      </c>
+      <c r="M29" s="8">
         <f t="shared" si="12"/>
-        <v>0.37050470250008927</v>
-      </c>
-      <c r="L29" s="5">
-        <f t="shared" si="13"/>
-        <v>7.4100940500017851E-2</v>
-      </c>
-      <c r="M29" s="8">
-        <f t="shared" si="14"/>
         <v>0.40195716766698691</v>
       </c>
       <c r="N29" s="8">
@@ -3603,15 +3603,15 @@
         <v>-0.20539415902870484</v>
       </c>
       <c r="Q29" s="2">
+        <f t="shared" si="13"/>
+        <v>109.98478009964276</v>
+      </c>
+      <c r="R29" s="9">
+        <f t="shared" si="14"/>
+        <v>-1.5219900357237262E-2</v>
+      </c>
+      <c r="S29" s="9">
         <f t="shared" si="15"/>
-        <v>109.98478009964276</v>
-      </c>
-      <c r="R29" s="9">
-        <f t="shared" si="16"/>
-        <v>-1.5219900357237262E-2</v>
-      </c>
-      <c r="S29" s="9">
-        <f t="shared" si="17"/>
         <v>109.96956019928552</v>
       </c>
       <c r="T29" s="9">
@@ -3643,15 +3643,15 @@
         <v>47.110135782068824</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.92456225122323898</v>
       </c>
       <c r="AB29" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>3.8613850187499716</v>
       </c>
     </row>
-    <row r="30" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="30" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
         <v>110</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>2700</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D30" s="4">
@@ -3678,23 +3678,23 @@
         <v>1.4146225178650775</v>
       </c>
       <c r="I30" s="5">
+        <f t="shared" si="8"/>
+        <v>8.9612598987990719E-2</v>
+      </c>
+      <c r="J30" s="5">
+        <f t="shared" si="9"/>
+        <v>0.30369242595094009</v>
+      </c>
+      <c r="K30" s="5">
         <f t="shared" si="10"/>
-        <v>8.9612598987990719E-2</v>
-      </c>
-      <c r="J30" s="5">
+        <v>0.39330502493893083</v>
+      </c>
+      <c r="L30" s="5">
         <f t="shared" si="11"/>
-        <v>0.30369242595094009</v>
-      </c>
-      <c r="K30" s="5">
+        <v>7.8661004987786165E-2</v>
+      </c>
+      <c r="M30" s="8">
         <f t="shared" si="12"/>
-        <v>0.39330502493893083</v>
-      </c>
-      <c r="L30" s="5">
-        <f t="shared" si="13"/>
-        <v>7.8661004987786165E-2</v>
-      </c>
-      <c r="M30" s="8">
-        <f t="shared" si="14"/>
         <v>0.64501998420917561</v>
       </c>
       <c r="N30" s="8">
@@ -3710,15 +3710,15 @@
         <v>-0.9567551862702437</v>
       </c>
       <c r="Q30" s="2">
+        <f t="shared" si="13"/>
+        <v>109.92474067552071</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="14"/>
+        <v>-7.5259324479293926E-2</v>
+      </c>
+      <c r="S30" s="9">
         <f t="shared" si="15"/>
-        <v>109.92474067552071</v>
-      </c>
-      <c r="R30" s="9">
-        <f t="shared" si="16"/>
-        <v>-7.5259324479293926E-2</v>
-      </c>
-      <c r="S30" s="9">
-        <f t="shared" si="17"/>
         <v>109.84948135104142</v>
       </c>
       <c r="T30" s="9">
@@ -3750,15 +3750,15 @@
         <v>56.079710800712711</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.77805448471899774</v>
       </c>
       <c r="AB30" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>2.9629454216307285</v>
       </c>
     </row>
-    <row r="31" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="31" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
         <v>110</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>2700</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D31" s="4">
@@ -3785,23 +3785,23 @@
         <v>0.98497708817883634</v>
       </c>
       <c r="I31" s="5">
+        <f t="shared" si="8"/>
+        <v>0.14396552085052172</v>
+      </c>
+      <c r="J31" s="5">
+        <f t="shared" si="9"/>
+        <v>0.60418786881251607</v>
+      </c>
+      <c r="K31" s="5">
         <f t="shared" si="10"/>
-        <v>0.14396552085052172</v>
-      </c>
-      <c r="J31" s="5">
+        <v>0.74815338966303779</v>
+      </c>
+      <c r="L31" s="5">
         <f t="shared" si="11"/>
-        <v>0.60418786881251607</v>
-      </c>
-      <c r="K31" s="5">
+        <v>0.14963067793260756</v>
+      </c>
+      <c r="M31" s="8">
         <f t="shared" si="12"/>
-        <v>0.74815338966303779</v>
-      </c>
-      <c r="L31" s="5">
-        <f t="shared" si="13"/>
-        <v>0.14963067793260756</v>
-      </c>
-      <c r="M31" s="8">
-        <f t="shared" si="14"/>
         <v>0.7905465212300028</v>
       </c>
       <c r="N31" s="8">
@@ -3817,15 +3817,15 @@
         <v>-1.3462514512691577</v>
       </c>
       <c r="Q31" s="2">
+        <f t="shared" si="13"/>
+        <v>109.79855948267884</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.20144051732116086</v>
+      </c>
+      <c r="S31" s="9">
         <f t="shared" si="15"/>
-        <v>109.79855948267884</v>
-      </c>
-      <c r="R31" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.20144051732116086</v>
-      </c>
-      <c r="S31" s="9">
-        <f t="shared" si="17"/>
         <v>109.59711896535768</v>
       </c>
       <c r="T31" s="9">
@@ -3857,15 +3857,15 @@
         <v>73.400097267167837</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.86418185426789651</v>
       </c>
       <c r="AB31" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>3.4459783598187648</v>
       </c>
     </row>
-    <row r="32" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="32" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
         <v>110</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>2700</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D32" s="4">
@@ -3892,23 +3892,23 @@
         <v>1.4536750389229482</v>
       </c>
       <c r="I32" s="5">
+        <f t="shared" si="8"/>
+        <v>0.11585823241307544</v>
+      </c>
+      <c r="J32" s="5">
+        <f t="shared" si="9"/>
+        <v>0.49687836839902183</v>
+      </c>
+      <c r="K32" s="5">
         <f t="shared" si="10"/>
-        <v>0.11585823241307544</v>
-      </c>
-      <c r="J32" s="5">
+        <v>0.61273660081209724</v>
+      </c>
+      <c r="L32" s="5">
         <f t="shared" si="11"/>
-        <v>0.49687836839902183</v>
-      </c>
-      <c r="K32" s="5">
+        <v>0.12254732016241945</v>
+      </c>
+      <c r="M32" s="8">
         <f t="shared" si="12"/>
-        <v>0.61273660081209724</v>
-      </c>
-      <c r="L32" s="5">
-        <f t="shared" si="13"/>
-        <v>0.12254732016241945</v>
-      </c>
-      <c r="M32" s="8">
-        <f t="shared" si="14"/>
         <v>0.77838511021638657</v>
       </c>
       <c r="N32" s="8">
@@ -3924,15 +3924,15 @@
         <v>-1.1023493242246258</v>
       </c>
       <c r="Q32" s="2">
+        <f t="shared" si="13"/>
+        <v>109.8649100444334</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13508995556658196</v>
+      </c>
+      <c r="S32" s="9">
         <f t="shared" si="15"/>
-        <v>109.8649100444334</v>
-      </c>
-      <c r="R32" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13508995556658196</v>
-      </c>
-      <c r="S32" s="9">
-        <f t="shared" si="17"/>
         <v>109.72982008886682</v>
       </c>
       <c r="T32" s="9">
@@ -3964,15 +3964,15 @@
         <v>55.095377997797605</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.0265553200147117</v>
       </c>
       <c r="AB32" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>4.7724291526210934</v>
       </c>
     </row>
-    <row r="33" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="33" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
         <v>110</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>2700</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D33" s="4">
@@ -3999,23 +3999,23 @@
         <v>1.9288314556401174</v>
       </c>
       <c r="I33" s="5">
+        <f t="shared" si="8"/>
+        <v>5.6338731062792108E-2</v>
+      </c>
+      <c r="J33" s="5">
+        <f t="shared" si="9"/>
+        <v>0.32736666953155413</v>
+      </c>
+      <c r="K33" s="5">
         <f t="shared" si="10"/>
-        <v>5.6338731062792108E-2</v>
-      </c>
-      <c r="J33" s="5">
+        <v>0.38370540059434621</v>
+      </c>
+      <c r="L33" s="5">
         <f t="shared" si="11"/>
-        <v>0.32736666953155413</v>
-      </c>
-      <c r="K33" s="5">
+        <v>7.6741080118869251E-2</v>
+      </c>
+      <c r="M33" s="8">
         <f t="shared" si="12"/>
-        <v>0.38370540059434621</v>
-      </c>
-      <c r="L33" s="5">
-        <f t="shared" si="13"/>
-        <v>7.6741080118869251E-2</v>
-      </c>
-      <c r="M33" s="8">
-        <f t="shared" si="14"/>
         <v>0.50287612202215182</v>
       </c>
       <c r="N33" s="8">
@@ -4031,15 +4031,15 @@
         <v>-0.50860816126913067</v>
       </c>
       <c r="Q33" s="2">
+        <f t="shared" si="13"/>
+        <v>109.96096886034694</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="14"/>
+        <v>-3.9031139653065129E-2</v>
+      </c>
+      <c r="S33" s="9">
         <f t="shared" si="15"/>
-        <v>109.96096886034694</v>
-      </c>
-      <c r="R33" s="9">
-        <f t="shared" si="16"/>
-        <v>-3.9031139653065129E-2</v>
-      </c>
-      <c r="S33" s="9">
-        <f t="shared" si="17"/>
         <v>109.92193772069388</v>
       </c>
       <c r="T33" s="9">
@@ -4071,15 +4071,15 @@
         <v>18.28841048255612</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>1.123540707872998</v>
       </c>
       <c r="AB33" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>6.0241546906946501</v>
       </c>
     </row>
-    <row r="34" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="34" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
         <v>110</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>2700</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D34" s="4">
@@ -4106,23 +4106,23 @@
         <v>1.5009967635341526</v>
       </c>
       <c r="I34" s="5">
+        <f t="shared" si="8"/>
+        <v>9.6866873254927668E-2</v>
+      </c>
+      <c r="J34" s="5">
+        <f t="shared" si="9"/>
+        <v>0.40759835712693959</v>
+      </c>
+      <c r="K34" s="5">
         <f t="shared" si="10"/>
-        <v>9.6866873254927668E-2</v>
-      </c>
-      <c r="J34" s="5">
+        <v>0.5044652303818673</v>
+      </c>
+      <c r="L34" s="5">
         <f t="shared" si="11"/>
-        <v>0.40759835712693959</v>
-      </c>
-      <c r="K34" s="5">
+        <v>0.10089304607637346</v>
+      </c>
+      <c r="M34" s="8">
         <f t="shared" si="12"/>
-        <v>0.5044652303818673</v>
-      </c>
-      <c r="L34" s="5">
-        <f t="shared" si="13"/>
-        <v>0.10089304607637346</v>
-      </c>
-      <c r="M34" s="8">
-        <f t="shared" si="14"/>
         <v>0.90934281773916803</v>
       </c>
       <c r="N34" s="8">
@@ -4138,15 +4138,15 @@
         <v>-1.3071492265478941</v>
       </c>
       <c r="Q34" s="2">
+        <f t="shared" si="13"/>
+        <v>109.8681177328572</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13188226714279261</v>
+      </c>
+      <c r="S34" s="9">
         <f t="shared" si="15"/>
-        <v>109.8681177328572</v>
-      </c>
-      <c r="R34" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13188226714279261</v>
-      </c>
-      <c r="S34" s="9">
-        <f t="shared" si="17"/>
         <v>109.7362354657144</v>
       </c>
       <c r="T34" s="9">
@@ -4186,7 +4186,7 @@
         <v>2.8395323978869609</v>
       </c>
     </row>
-    <row r="35" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="35" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
         <v>110</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>2700</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D35" s="4">
@@ -4213,23 +4213,23 @@
         <v>0.96458156371424908</v>
       </c>
       <c r="I35" s="5">
+        <f t="shared" si="8"/>
+        <v>0.18730162307756013</v>
+      </c>
+      <c r="J35" s="5">
+        <f t="shared" si="9"/>
+        <v>0.57677632100719445</v>
+      </c>
+      <c r="K35" s="5">
         <f t="shared" si="10"/>
-        <v>0.18730162307756013</v>
-      </c>
-      <c r="J35" s="5">
+        <v>0.7640779440847546</v>
+      </c>
+      <c r="L35" s="5">
         <f t="shared" si="11"/>
-        <v>0.57677632100719445</v>
-      </c>
-      <c r="K35" s="5">
+        <v>0.15281558881695093</v>
+      </c>
+      <c r="M35" s="8">
         <f t="shared" si="12"/>
-        <v>0.7640779440847546</v>
-      </c>
-      <c r="L35" s="5">
-        <f t="shared" si="13"/>
-        <v>0.15281558881695093</v>
-      </c>
-      <c r="M35" s="8">
-        <f t="shared" si="14"/>
         <v>0.63539268709204366</v>
       </c>
       <c r="N35" s="8">
@@ -4245,15 +4245,15 @@
         <v>-1.1897583793490274</v>
       </c>
       <c r="Q35" s="2">
+        <f t="shared" si="13"/>
+        <v>109.81818637270989</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.18181362729012288</v>
+      </c>
+      <c r="S35" s="9">
         <f t="shared" si="15"/>
-        <v>109.81818637270989</v>
-      </c>
-      <c r="R35" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.18181362729012288</v>
-      </c>
-      <c r="S35" s="9">
-        <f t="shared" si="17"/>
         <v>109.63637274541976</v>
       </c>
       <c r="T35" s="9">
@@ -4293,7 +4293,7 @@
         <v>3.1056855158964205</v>
       </c>
     </row>
-    <row r="36" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="36" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
         <v>110</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>2700</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D36" s="4">
@@ -4320,23 +4320,23 @@
         <v>1.5076331871163318</v>
       </c>
       <c r="I36" s="5">
+        <f t="shared" si="8"/>
+        <v>0.12085325658776644</v>
+      </c>
+      <c r="J36" s="5">
+        <f t="shared" si="9"/>
+        <v>0.38633394776476043</v>
+      </c>
+      <c r="K36" s="5">
         <f t="shared" si="10"/>
-        <v>0.12085325658776644</v>
-      </c>
-      <c r="J36" s="5">
+        <v>0.50718720435252684</v>
+      </c>
+      <c r="L36" s="5">
         <f t="shared" si="11"/>
-        <v>0.38633394776476043</v>
-      </c>
-      <c r="K36" s="5">
+        <v>0.10143744087050538</v>
+      </c>
+      <c r="M36" s="8">
         <f t="shared" si="12"/>
-        <v>0.50718720435252684</v>
-      </c>
-      <c r="L36" s="5">
-        <f t="shared" si="13"/>
-        <v>0.10143744087050538</v>
-      </c>
-      <c r="M36" s="8">
-        <f t="shared" si="14"/>
         <v>0.81945481253063024</v>
       </c>
       <c r="N36" s="8">
@@ -4352,15 +4352,15 @@
         <v>-1.272573097793317</v>
       </c>
       <c r="Q36" s="2">
+        <f t="shared" si="13"/>
+        <v>109.8709134416392</v>
+      </c>
+      <c r="R36" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.12908655836080546</v>
+      </c>
+      <c r="S36" s="9">
         <f t="shared" si="15"/>
-        <v>109.8709134416392</v>
-      </c>
-      <c r="R36" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.12908655836080546</v>
-      </c>
-      <c r="S36" s="9">
-        <f t="shared" si="17"/>
         <v>109.74182688327839</v>
       </c>
       <c r="T36" s="9">
@@ -4400,7 +4400,7 @@
         <v>2.4017751570025787</v>
       </c>
     </row>
-    <row r="37" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="37" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A37" s="2">
         <v>110</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>2700</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D37" s="4">
@@ -4427,23 +4427,23 @@
         <v>1.3638890314436041</v>
       </c>
       <c r="I37" s="5">
+        <f t="shared" si="8"/>
+        <v>0.15343626077981143</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="9"/>
+        <v>0.5851124673779452</v>
+      </c>
+      <c r="K37" s="5">
         <f t="shared" si="10"/>
-        <v>0.15343626077981143</v>
-      </c>
-      <c r="J37" s="5">
+        <v>0.73854872815775663</v>
+      </c>
+      <c r="L37" s="5">
         <f t="shared" si="11"/>
-        <v>0.5851124673779452</v>
-      </c>
-      <c r="K37" s="5">
+        <v>0.14770974563155134</v>
+      </c>
+      <c r="M37" s="8">
         <f t="shared" si="12"/>
-        <v>0.73854872815775663</v>
-      </c>
-      <c r="L37" s="5">
-        <f t="shared" si="13"/>
-        <v>0.14770974563155134</v>
-      </c>
-      <c r="M37" s="8">
-        <f t="shared" si="14"/>
         <v>0.84726484345082653</v>
       </c>
       <c r="N37" s="8">
@@ -4459,15 +4459,15 @@
         <v>-1.3358761990174104</v>
       </c>
       <c r="Q37" s="2">
+        <f t="shared" si="13"/>
+        <v>109.8026780664479</v>
+      </c>
+      <c r="R37" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.19732193355210534</v>
+      </c>
+      <c r="S37" s="9">
         <f t="shared" si="15"/>
-        <v>109.8026780664479</v>
-      </c>
-      <c r="R37" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.19732193355210534</v>
-      </c>
-      <c r="S37" s="9">
-        <f t="shared" si="17"/>
         <v>109.60535613289579</v>
       </c>
       <c r="T37" s="9">
@@ -4507,7 +4507,7 @@
         <v>2.0767083769327317</v>
       </c>
     </row>
-    <row r="38" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="38" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
         <v>110</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>2700</v>
       </c>
       <c r="C38" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D38" s="4">
@@ -4534,23 +4534,23 @@
         <v>1.1274845005207037</v>
       </c>
       <c r="I38" s="5">
+        <f t="shared" si="8"/>
+        <v>4.491936148305109E-2</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" si="9"/>
+        <v>0.18217230034574977</v>
+      </c>
+      <c r="K38" s="5">
         <f t="shared" si="10"/>
-        <v>4.491936148305109E-2</v>
-      </c>
-      <c r="J38" s="5">
+        <v>0.22709166182880086</v>
+      </c>
+      <c r="L38" s="5">
         <f t="shared" si="11"/>
-        <v>0.18217230034574977</v>
-      </c>
-      <c r="K38" s="5">
+        <v>4.5418332365760178E-2</v>
+      </c>
+      <c r="M38" s="8">
         <f t="shared" si="12"/>
-        <v>0.22709166182880086</v>
-      </c>
-      <c r="L38" s="5">
-        <f t="shared" si="13"/>
-        <v>4.5418332365760178E-2</v>
-      </c>
-      <c r="M38" s="8">
-        <f t="shared" si="14"/>
         <v>0.54560719523489154</v>
       </c>
       <c r="N38" s="8">
@@ -4566,15 +4566,15 @@
         <v>-0.81788180703560931</v>
       </c>
       <c r="Q38" s="2">
+        <f t="shared" si="13"/>
+        <v>109.96285317225215</v>
+      </c>
+      <c r="R38" s="9">
+        <f t="shared" si="14"/>
+        <v>-3.7146827747851836E-2</v>
+      </c>
+      <c r="S38" s="9">
         <f t="shared" si="15"/>
-        <v>109.96285317225215</v>
-      </c>
-      <c r="R38" s="9">
-        <f t="shared" si="16"/>
-        <v>-3.7146827747851836E-2</v>
-      </c>
-      <c r="S38" s="9">
-        <f t="shared" si="17"/>
         <v>109.92570634450431</v>
       </c>
       <c r="T38" s="9">
@@ -4614,7 +4614,7 @@
         <v>6.8183490843750132</v>
       </c>
     </row>
-    <row r="39" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="39" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
         <v>110</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>2700</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D39" s="4">
@@ -4641,23 +4641,23 @@
         <v>0.84882539129575851</v>
       </c>
       <c r="I39" s="5">
+        <f t="shared" si="8"/>
+        <v>4.6712689917200026E-2</v>
+      </c>
+      <c r="J39" s="5">
+        <f t="shared" si="9"/>
+        <v>0.15307918309198809</v>
+      </c>
+      <c r="K39" s="5">
         <f t="shared" si="10"/>
-        <v>4.6712689917200026E-2</v>
-      </c>
-      <c r="J39" s="5">
+        <v>0.1997918730091881</v>
+      </c>
+      <c r="L39" s="5">
         <f t="shared" si="11"/>
-        <v>0.15307918309198809</v>
-      </c>
-      <c r="K39" s="5">
+        <v>3.9958374601837626E-2</v>
+      </c>
+      <c r="M39" s="8">
         <f t="shared" si="12"/>
-        <v>0.1997918730091881</v>
-      </c>
-      <c r="L39" s="5">
-        <f t="shared" si="13"/>
-        <v>3.9958374601837626E-2</v>
-      </c>
-      <c r="M39" s="8">
-        <f t="shared" si="14"/>
         <v>0.46501056559677323</v>
       </c>
       <c r="N39" s="8">
@@ -4673,15 +4673,15 @@
         <v>-0.4850322882103939</v>
       </c>
       <c r="Q39" s="2">
+        <f t="shared" si="13"/>
+        <v>109.9806188981337</v>
+      </c>
+      <c r="R39" s="9">
+        <f t="shared" si="14"/>
+        <v>-1.9381101866297393E-2</v>
+      </c>
+      <c r="S39" s="9">
         <f t="shared" si="15"/>
-        <v>109.9806188981337</v>
-      </c>
-      <c r="R39" s="9">
-        <f t="shared" si="16"/>
-        <v>-1.9381101866297393E-2</v>
-      </c>
-      <c r="S39" s="9">
-        <f t="shared" si="17"/>
         <v>109.9612377962674</v>
       </c>
       <c r="T39" s="9">
@@ -4721,7 +4721,7 @@
         <v>30.944347830063769</v>
       </c>
     </row>
-    <row r="40" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="40" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A40" s="2">
         <v>110</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>2700</v>
       </c>
       <c r="C40" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D40" s="4">
@@ -4748,23 +4748,23 @@
         <v>1.1339905688634642</v>
       </c>
       <c r="I40" s="5">
+        <f t="shared" si="8"/>
+        <v>0.18301546633043037</v>
+      </c>
+      <c r="J40" s="5">
+        <f t="shared" si="9"/>
+        <v>0.86269223851173749</v>
+      </c>
+      <c r="K40" s="5">
         <f t="shared" si="10"/>
-        <v>0.18301546633043037</v>
-      </c>
-      <c r="J40" s="5">
+        <v>1.0457077048421679</v>
+      </c>
+      <c r="L40" s="5">
         <f t="shared" si="11"/>
-        <v>0.86269223851173749</v>
-      </c>
-      <c r="K40" s="5">
+        <v>0.2091415409684336</v>
+      </c>
+      <c r="M40" s="8">
         <f t="shared" si="12"/>
-        <v>1.0457077048421679</v>
-      </c>
-      <c r="L40" s="5">
-        <f t="shared" si="13"/>
-        <v>0.2091415409684336</v>
-      </c>
-      <c r="M40" s="8">
-        <f t="shared" si="14"/>
         <v>0.77010231915140326</v>
       </c>
       <c r="N40" s="8">
@@ -4780,15 +4780,15 @@
         <v>-1.1565718744499813</v>
       </c>
       <c r="Q40" s="2">
+        <f t="shared" si="13"/>
+        <v>109.75811277593678</v>
+      </c>
+      <c r="R40" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.2418872240632188</v>
+      </c>
+      <c r="S40" s="9">
         <f t="shared" si="15"/>
-        <v>109.75811277593678</v>
-      </c>
-      <c r="R40" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.2418872240632188</v>
-      </c>
-      <c r="S40" s="9">
-        <f t="shared" si="17"/>
         <v>109.51622555187356</v>
       </c>
       <c r="T40" s="9">
@@ -4828,7 +4828,7 @@
         <v>13.052646885623773</v>
       </c>
     </row>
-    <row r="41" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="41" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A41" s="2">
         <v>110</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>2700</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D41" s="4">
@@ -4855,23 +4855,23 @@
         <v>1.7311206552399343</v>
       </c>
       <c r="I41" s="5">
+        <f t="shared" si="8"/>
+        <v>8.5407453295768154E-2</v>
+      </c>
+      <c r="J41" s="5">
+        <f t="shared" si="9"/>
+        <v>0.31030887783626943</v>
+      </c>
+      <c r="K41" s="5">
         <f t="shared" si="10"/>
-        <v>8.5407453295768154E-2</v>
-      </c>
-      <c r="J41" s="5">
+        <v>0.39571633113203758</v>
+      </c>
+      <c r="L41" s="5">
         <f t="shared" si="11"/>
-        <v>0.31030887783626943</v>
-      </c>
-      <c r="K41" s="5">
+        <v>7.9143266226407522E-2</v>
+      </c>
+      <c r="M41" s="8">
         <f t="shared" si="12"/>
-        <v>0.39571633113203758</v>
-      </c>
-      <c r="L41" s="5">
-        <f t="shared" si="13"/>
-        <v>7.9143266226407522E-2</v>
-      </c>
-      <c r="M41" s="8">
-        <f t="shared" si="14"/>
         <v>0.90259303458681694</v>
       </c>
       <c r="N41" s="8">
@@ -4887,15 +4887,15 @@
         <v>-1.3110514875573409</v>
       </c>
       <c r="Q41" s="2">
+        <f t="shared" si="13"/>
+        <v>109.8962391030837</v>
+      </c>
+      <c r="R41" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.10376089691627824</v>
+      </c>
+      <c r="S41" s="9">
         <f t="shared" si="15"/>
-        <v>109.8962391030837</v>
-      </c>
-      <c r="R41" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.10376089691627824</v>
-      </c>
-      <c r="S41" s="9">
-        <f t="shared" si="17"/>
         <v>109.79247820616742</v>
       </c>
       <c r="T41" s="9">
@@ -4935,7 +4935,7 @@
         <v>1.9079106479327654</v>
       </c>
     </row>
-    <row r="42" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="42" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A42" s="2">
         <v>110</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>2700</v>
       </c>
       <c r="C42" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D42" s="4">
@@ -4962,23 +4962,23 @@
         <v>1.487868200618095</v>
       </c>
       <c r="I42" s="5">
+        <f t="shared" si="8"/>
+        <v>4.5210832917006845E-2</v>
+      </c>
+      <c r="J42" s="5">
+        <f t="shared" si="9"/>
+        <v>0.38396024910028576</v>
+      </c>
+      <c r="K42" s="5">
         <f t="shared" si="10"/>
-        <v>4.5210832917006845E-2</v>
-      </c>
-      <c r="J42" s="5">
+        <v>0.42917108201729259</v>
+      </c>
+      <c r="L42" s="5">
         <f t="shared" si="11"/>
-        <v>0.38396024910028576</v>
-      </c>
-      <c r="K42" s="5">
+        <v>8.5834216403458521E-2</v>
+      </c>
+      <c r="M42" s="8">
         <f t="shared" si="12"/>
-        <v>0.42917108201729259</v>
-      </c>
-      <c r="L42" s="5">
-        <f t="shared" si="13"/>
-        <v>8.5834216403458521E-2</v>
-      </c>
-      <c r="M42" s="8">
-        <f t="shared" si="14"/>
         <v>0.73758678860491411</v>
       </c>
       <c r="N42" s="8">
@@ -4994,15 +4994,15 @@
         <v>-0.68085313625698951</v>
       </c>
       <c r="Q42" s="2">
+        <f t="shared" si="13"/>
+        <v>109.94155950456356</v>
+      </c>
+      <c r="R42" s="9">
+        <f t="shared" si="14"/>
+        <v>-5.8440495436455867E-2</v>
+      </c>
+      <c r="S42" s="9">
         <f t="shared" si="15"/>
-        <v>109.94155950456356</v>
-      </c>
-      <c r="R42" s="9">
-        <f t="shared" si="16"/>
-        <v>-5.8440495436455867E-2</v>
-      </c>
-      <c r="S42" s="9">
-        <f t="shared" si="17"/>
         <v>109.8831190091271</v>
       </c>
       <c r="T42" s="9">
@@ -5042,7 +5042,7 @@
         <v>4.4131750295194188</v>
       </c>
     </row>
-    <row r="43" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="43" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A43" s="2">
         <v>110</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>2700</v>
       </c>
       <c r="C43" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D43" s="4">
@@ -5069,23 +5069,23 @@
         <v>1.1181612058590542</v>
       </c>
       <c r="I43" s="5">
+        <f t="shared" si="8"/>
+        <v>0.1249437957381294</v>
+      </c>
+      <c r="J43" s="5">
+        <f t="shared" si="9"/>
+        <v>0.49574553914381292</v>
+      </c>
+      <c r="K43" s="5">
         <f t="shared" si="10"/>
-        <v>0.1249437957381294</v>
-      </c>
-      <c r="J43" s="5">
+        <v>0.62068933488194233</v>
+      </c>
+      <c r="L43" s="5">
         <f t="shared" si="11"/>
-        <v>0.49574553914381292</v>
-      </c>
-      <c r="K43" s="5">
+        <v>0.12413786697638847</v>
+      </c>
+      <c r="M43" s="8">
         <f t="shared" si="12"/>
-        <v>0.62068933488194233</v>
-      </c>
-      <c r="L43" s="5">
-        <f t="shared" si="13"/>
-        <v>0.12413786697638847</v>
-      </c>
-      <c r="M43" s="8">
-        <f t="shared" si="14"/>
         <v>0.42904739531103619</v>
       </c>
       <c r="N43" s="8">
@@ -5101,15 +5101,15 @@
         <v>-0.66493907174687095</v>
       </c>
       <c r="Q43" s="2">
+        <f t="shared" si="13"/>
+        <v>109.91745588196409</v>
+      </c>
+      <c r="R43" s="9">
+        <f t="shared" si="14"/>
+        <v>-8.2544118035916297E-2</v>
+      </c>
+      <c r="S43" s="9">
         <f t="shared" si="15"/>
-        <v>109.91745588196409</v>
-      </c>
-      <c r="R43" s="9">
-        <f t="shared" si="16"/>
-        <v>-8.2544118035916297E-2</v>
-      </c>
-      <c r="S43" s="9">
-        <f t="shared" si="17"/>
         <v>109.83491176392818</v>
       </c>
       <c r="T43" s="9">
@@ -5149,7 +5149,7 @@
         <v>2.1742801726569714</v>
       </c>
     </row>
-    <row r="44" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="44" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A44" s="2">
         <v>110</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>2700</v>
       </c>
       <c r="C44" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D44" s="4">
@@ -5176,23 +5176,23 @@
         <v>1.6798646039034322</v>
       </c>
       <c r="I44" s="5">
+        <f t="shared" si="8"/>
+        <v>0.14184695115922177</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.53803564016450678</v>
+      </c>
+      <c r="K44" s="5">
         <f t="shared" si="10"/>
-        <v>0.14184695115922177</v>
-      </c>
-      <c r="J44" s="5">
+        <v>0.67988259132372852</v>
+      </c>
+      <c r="L44" s="5">
         <f t="shared" si="11"/>
-        <v>0.53803564016450678</v>
-      </c>
-      <c r="K44" s="5">
+        <v>0.13597651826474572</v>
+      </c>
+      <c r="M44" s="8">
         <f t="shared" si="12"/>
-        <v>0.67988259132372852</v>
-      </c>
-      <c r="L44" s="5">
-        <f t="shared" si="13"/>
-        <v>0.13597651826474572</v>
-      </c>
-      <c r="M44" s="8">
-        <f t="shared" si="14"/>
         <v>0.69965978242374871</v>
       </c>
       <c r="N44" s="8">
@@ -5208,15 +5208,15 @@
         <v>-0.99411709697838591</v>
       </c>
       <c r="Q44" s="2">
+        <f t="shared" si="13"/>
+        <v>109.86482341840542</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13517658159457749</v>
+      </c>
+      <c r="S44" s="9">
         <f t="shared" si="15"/>
-        <v>109.86482341840542</v>
-      </c>
-      <c r="R44" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13517658159457749</v>
-      </c>
-      <c r="S44" s="9">
-        <f t="shared" si="17"/>
         <v>109.72964683681084</v>
       </c>
       <c r="T44" s="9">
@@ -5256,7 +5256,7 @@
         <v>2.1181800291469823</v>
       </c>
     </row>
-    <row r="45" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="45" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A45" s="2">
         <v>110</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>2700</v>
       </c>
       <c r="C45" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D45" s="4">
@@ -5283,23 +5283,23 @@
         <v>2.0070688022492282</v>
       </c>
       <c r="I45" s="5">
+        <f t="shared" si="8"/>
+        <v>4.8740825510921522E-2</v>
+      </c>
+      <c r="J45" s="5">
+        <f t="shared" si="9"/>
+        <v>0.6590989579044596</v>
+      </c>
+      <c r="K45" s="5">
         <f t="shared" si="10"/>
-        <v>4.8740825510921522E-2</v>
-      </c>
-      <c r="J45" s="5">
+        <v>0.70783978341538112</v>
+      </c>
+      <c r="L45" s="5">
         <f t="shared" si="11"/>
-        <v>0.6590989579044596</v>
-      </c>
-      <c r="K45" s="5">
+        <v>0.14156795668307623</v>
+      </c>
+      <c r="M45" s="8">
         <f t="shared" si="12"/>
-        <v>0.70783978341538112</v>
-      </c>
-      <c r="L45" s="5">
-        <f t="shared" si="13"/>
-        <v>0.14156795668307623</v>
-      </c>
-      <c r="M45" s="8">
-        <f t="shared" si="14"/>
         <v>0.82428683955890736</v>
       </c>
       <c r="N45" s="8">
@@ -5315,15 +5315,15 @@
         <v>-0.45813942248314699</v>
       </c>
       <c r="Q45" s="2">
+        <f t="shared" si="13"/>
+        <v>109.93514213808311</v>
+      </c>
+      <c r="R45" s="9">
+        <f t="shared" si="14"/>
+        <v>-6.4857861916903708E-2</v>
+      </c>
+      <c r="S45" s="9">
         <f t="shared" si="15"/>
-        <v>109.93514213808311</v>
-      </c>
-      <c r="R45" s="9">
-        <f t="shared" si="16"/>
-        <v>-6.4857861916903708E-2</v>
-      </c>
-      <c r="S45" s="9">
-        <f t="shared" si="17"/>
         <v>109.8702842761662</v>
       </c>
       <c r="T45" s="9">
@@ -5363,7 +5363,7 @@
         <v>6.8672800993533158</v>
       </c>
     </row>
-    <row r="46" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="46" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A46" s="2">
         <v>110</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>2700</v>
       </c>
       <c r="C46" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D46" s="4">
@@ -5390,23 +5390,23 @@
         <v>1.8088290026490512</v>
       </c>
       <c r="I46" s="5">
+        <f t="shared" si="8"/>
+        <v>0.1258457445776669</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="9"/>
+        <v>0.78712729263154524</v>
+      </c>
+      <c r="K46" s="5">
         <f t="shared" si="10"/>
-        <v>0.1258457445776669</v>
-      </c>
-      <c r="J46" s="5">
+        <v>0.91297303720921219</v>
+      </c>
+      <c r="L46" s="5">
         <f t="shared" si="11"/>
-        <v>0.78712729263154524</v>
-      </c>
-      <c r="K46" s="5">
+        <v>0.18259460744184244</v>
+      </c>
+      <c r="M46" s="8">
         <f t="shared" si="12"/>
-        <v>0.91297303720921219</v>
-      </c>
-      <c r="L46" s="5">
-        <f t="shared" si="13"/>
-        <v>0.18259460744184244</v>
-      </c>
-      <c r="M46" s="8">
-        <f t="shared" si="14"/>
         <v>0.73765823879172321</v>
       </c>
       <c r="N46" s="8">
@@ -5422,15 +5422,15 @@
         <v>-0.76517145339713488</v>
       </c>
       <c r="Q46" s="2">
+        <f t="shared" si="13"/>
+        <v>109.86028381884124</v>
+      </c>
+      <c r="R46" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.13971618115875389</v>
+      </c>
+      <c r="S46" s="9">
         <f t="shared" si="15"/>
-        <v>109.86028381884124</v>
-      </c>
-      <c r="R46" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.13971618115875389</v>
-      </c>
-      <c r="S46" s="9">
-        <f t="shared" si="17"/>
         <v>109.72056763768248</v>
       </c>
       <c r="T46" s="9">
@@ -5470,7 +5470,7 @@
         <v>12.834377588279862</v>
       </c>
     </row>
-    <row r="47" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="47" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="2">
         <v>110</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>2700</v>
       </c>
       <c r="C47" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D47" s="4">
@@ -5497,23 +5497,23 @@
         <v>1.1071680118677552</v>
       </c>
       <c r="I47" s="5">
+        <f t="shared" si="8"/>
+        <v>1.7946618872552358E-2</v>
+      </c>
+      <c r="J47" s="5">
+        <f t="shared" si="9"/>
+        <v>8.9880206390690914E-2</v>
+      </c>
+      <c r="K47" s="5">
         <f t="shared" si="10"/>
-        <v>1.7946618872552358E-2</v>
-      </c>
-      <c r="J47" s="5">
+        <v>0.10782682526324328</v>
+      </c>
+      <c r="L47" s="5">
         <f t="shared" si="11"/>
-        <v>8.9880206390690914E-2</v>
-      </c>
-      <c r="K47" s="5">
+        <v>2.1565365052648656E-2</v>
+      </c>
+      <c r="M47" s="8">
         <f t="shared" si="12"/>
-        <v>0.10782682526324328</v>
-      </c>
-      <c r="L47" s="5">
-        <f t="shared" si="13"/>
-        <v>2.1565365052648656E-2</v>
-      </c>
-      <c r="M47" s="8">
-        <f t="shared" si="14"/>
         <v>0.3359256887000639</v>
       </c>
       <c r="N47" s="8">
@@ -5529,15 +5529,15 @@
         <v>-0.41570911184377968</v>
       </c>
       <c r="Q47" s="2">
+        <f t="shared" si="13"/>
+        <v>109.99103508124738</v>
+      </c>
+      <c r="R47" s="9">
+        <f t="shared" si="14"/>
+        <v>-8.9649187526234572E-3</v>
+      </c>
+      <c r="S47" s="9">
         <f t="shared" si="15"/>
-        <v>109.99103508124738</v>
-      </c>
-      <c r="R47" s="9">
-        <f t="shared" si="16"/>
-        <v>-8.9649187526234572E-3</v>
-      </c>
-      <c r="S47" s="9">
-        <f t="shared" si="17"/>
         <v>109.98207016249475</v>
       </c>
       <c r="T47" s="9">
@@ -5577,7 +5577,7 @@
         <v>4.3202928878722267</v>
       </c>
     </row>
-    <row r="48" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="48" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="2">
         <v>110</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>2700</v>
       </c>
       <c r="C48" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D48" s="4">
@@ -5604,23 +5604,23 @@
         <v>1.6872861945232924</v>
       </c>
       <c r="I48" s="5">
+        <f t="shared" si="8"/>
+        <v>0.16770012661200778</v>
+      </c>
+      <c r="J48" s="5">
+        <f t="shared" si="9"/>
+        <v>0.74579211549568103</v>
+      </c>
+      <c r="K48" s="5">
         <f t="shared" si="10"/>
-        <v>0.16770012661200778</v>
-      </c>
-      <c r="J48" s="5">
+        <v>0.91349224210768876</v>
+      </c>
+      <c r="L48" s="5">
         <f t="shared" si="11"/>
-        <v>0.74579211549568103</v>
-      </c>
-      <c r="K48" s="5">
+        <v>0.18269844842153776</v>
+      </c>
+      <c r="M48" s="8">
         <f t="shared" si="12"/>
-        <v>0.91349224210768876</v>
-      </c>
-      <c r="L48" s="5">
-        <f t="shared" si="13"/>
-        <v>0.18269844842153776</v>
-      </c>
-      <c r="M48" s="8">
-        <f t="shared" si="14"/>
         <v>0.84985503037720034</v>
       </c>
       <c r="N48" s="8">
@@ -5636,15 +5636,15 @@
         <v>-1.0936251455915569</v>
       </c>
       <c r="Q48" s="2">
+        <f t="shared" si="13"/>
+        <v>109.80019638274564</v>
+      </c>
+      <c r="R48" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.19980361725435578</v>
+      </c>
+      <c r="S48" s="9">
         <f t="shared" si="15"/>
-        <v>109.80019638274564</v>
-      </c>
-      <c r="R48" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.19980361725435578</v>
-      </c>
-      <c r="S48" s="9">
-        <f t="shared" si="17"/>
         <v>109.60039276549128</v>
       </c>
       <c r="T48" s="9">
@@ -5684,7 +5684,7 @@
         <v>7.1280081597772389</v>
       </c>
     </row>
-    <row r="49" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="49" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A49" s="2">
         <v>110</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>2700</v>
       </c>
       <c r="C49" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D49" s="4">
@@ -5711,23 +5711,23 @@
         <v>1.8474230601808819</v>
       </c>
       <c r="I49" s="5">
+        <f t="shared" si="8"/>
+        <v>7.8040398649079468E-2</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" si="9"/>
+        <v>0.38288603554028822</v>
+      </c>
+      <c r="K49" s="5">
         <f t="shared" si="10"/>
-        <v>7.8040398649079468E-2</v>
-      </c>
-      <c r="J49" s="5">
+        <v>0.46092643418936768</v>
+      </c>
+      <c r="L49" s="5">
         <f t="shared" si="11"/>
-        <v>0.38288603554028822</v>
-      </c>
-      <c r="K49" s="5">
+        <v>9.218528683787354E-2</v>
+      </c>
+      <c r="M49" s="8">
         <f t="shared" si="12"/>
-        <v>0.46092643418936768</v>
-      </c>
-      <c r="L49" s="5">
-        <f t="shared" si="13"/>
-        <v>9.218528683787354E-2</v>
-      </c>
-      <c r="M49" s="8">
-        <f t="shared" si="14"/>
         <v>0.61603427282508361</v>
       </c>
       <c r="N49" s="8">
@@ -5743,15 +5743,15 @@
         <v>-0.73881269704852959</v>
       </c>
       <c r="Q49" s="2">
+        <f t="shared" si="13"/>
+        <v>109.93189233960312</v>
+      </c>
+      <c r="R49" s="9">
+        <f t="shared" si="14"/>
+        <v>-6.8107660396881667E-2</v>
+      </c>
+      <c r="S49" s="9">
         <f t="shared" si="15"/>
-        <v>109.93189233960312</v>
-      </c>
-      <c r="R49" s="9">
-        <f t="shared" si="16"/>
-        <v>-6.8107660396881667E-2</v>
-      </c>
-      <c r="S49" s="9">
-        <f t="shared" si="17"/>
         <v>109.86378467920625</v>
       </c>
       <c r="T49" s="9">
@@ -5791,7 +5791,7 @@
         <v>2.4271612400630995</v>
       </c>
     </row>
-    <row r="50" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="50" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A50" s="2">
         <v>110</v>
       </c>
@@ -5799,7 +5799,7 @@
         <v>2700</v>
       </c>
       <c r="C50" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D50" s="4">
@@ -5818,23 +5818,23 @@
         <v>2.0245798239662838</v>
       </c>
       <c r="I50" s="5">
+        <f t="shared" si="8"/>
+        <v>0.1080957567532143</v>
+      </c>
+      <c r="J50" s="5">
+        <f t="shared" si="9"/>
+        <v>0.38925756989753324</v>
+      </c>
+      <c r="K50" s="5">
         <f t="shared" si="10"/>
-        <v>0.1080957567532143</v>
-      </c>
-      <c r="J50" s="5">
+        <v>0.49735332665074755</v>
+      </c>
+      <c r="L50" s="5">
         <f t="shared" si="11"/>
-        <v>0.38925756989753324</v>
-      </c>
-      <c r="K50" s="5">
+        <v>9.9470665330149519E-2</v>
+      </c>
+      <c r="M50" s="8">
         <f t="shared" si="12"/>
-        <v>0.49735332665074755</v>
-      </c>
-      <c r="L50" s="5">
-        <f t="shared" si="13"/>
-        <v>9.9470665330149519E-2</v>
-      </c>
-      <c r="M50" s="8">
-        <f t="shared" si="14"/>
         <v>0.68670943800411155</v>
       </c>
       <c r="N50" s="8">
@@ -5850,15 +5850,15 @@
         <v>-0.91618540675186966</v>
       </c>
       <c r="Q50" s="2">
+        <f t="shared" si="13"/>
+        <v>109.90886642802461</v>
+      </c>
+      <c r="R50" s="9">
+        <f t="shared" si="14"/>
+        <v>-9.1133571975382133E-2</v>
+      </c>
+      <c r="S50" s="9">
         <f t="shared" si="15"/>
-        <v>109.90886642802461</v>
-      </c>
-      <c r="R50" s="9">
-        <f t="shared" si="16"/>
-        <v>-9.1133571975382133E-2</v>
-      </c>
-      <c r="S50" s="9">
-        <f t="shared" si="17"/>
         <v>109.81773285604923</v>
       </c>
       <c r="T50" s="9">
@@ -5898,7 +5898,7 @@
         <v>1.9595990072284946</v>
       </c>
     </row>
-    <row r="51" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="51" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A51" s="2">
         <v>110</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>2700</v>
       </c>
       <c r="C51" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D51" s="4">
@@ -5925,23 +5925,23 @@
         <v>1.4568847634536204</v>
       </c>
       <c r="I51" s="5">
+        <f t="shared" si="8"/>
+        <v>0.10854315389302084</v>
+      </c>
+      <c r="J51" s="5">
+        <f t="shared" si="9"/>
+        <v>0.28252709653782748</v>
+      </c>
+      <c r="K51" s="5">
         <f t="shared" si="10"/>
-        <v>0.10854315389302084</v>
-      </c>
-      <c r="J51" s="5">
+        <v>0.39107025043084831</v>
+      </c>
+      <c r="L51" s="5">
         <f t="shared" si="11"/>
-        <v>0.28252709653782748</v>
-      </c>
-      <c r="K51" s="5">
+        <v>7.8214050086169662E-2</v>
+      </c>
+      <c r="M51" s="8">
         <f t="shared" si="12"/>
-        <v>0.39107025043084831</v>
-      </c>
-      <c r="L51" s="5">
-        <f t="shared" si="13"/>
-        <v>7.8214050086169662E-2</v>
-      </c>
-      <c r="M51" s="8">
-        <f t="shared" si="14"/>
         <v>0.60436038677790738</v>
       </c>
       <c r="N51" s="8">
@@ -5957,15 +5957,15 @@
         <v>-0.42281378282398341</v>
       </c>
       <c r="Q51" s="2">
+        <f t="shared" si="13"/>
+        <v>109.96693002161308</v>
+      </c>
+      <c r="R51" s="9">
+        <f t="shared" si="14"/>
+        <v>-3.30699783869179E-2</v>
+      </c>
+      <c r="S51" s="9">
         <f t="shared" si="15"/>
-        <v>109.96693002161308</v>
-      </c>
-      <c r="R51" s="9">
-        <f t="shared" si="16"/>
-        <v>-3.30699783869179E-2</v>
-      </c>
-      <c r="S51" s="9">
-        <f t="shared" si="17"/>
         <v>109.93386004322616</v>
       </c>
       <c r="T51" s="9">
@@ -6005,7 +6005,7 @@
         <v>3.583067644025888</v>
       </c>
     </row>
-    <row r="52" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="52" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
         <v>110</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>2700</v>
       </c>
       <c r="C52" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D52" s="4">
@@ -6032,23 +6032,23 @@
         <v>1.5411525431615343</v>
       </c>
       <c r="I52" s="5">
+        <f t="shared" si="8"/>
+        <v>0.25708693843481151</v>
+      </c>
+      <c r="J52" s="5">
+        <f t="shared" si="9"/>
+        <v>0.72404558290781995</v>
+      </c>
+      <c r="K52" s="5">
         <f t="shared" si="10"/>
-        <v>0.25708693843481151</v>
-      </c>
-      <c r="J52" s="5">
+        <v>0.9811325213426314</v>
+      </c>
+      <c r="L52" s="5">
         <f t="shared" si="11"/>
-        <v>0.72404558290781995</v>
-      </c>
-      <c r="K52" s="5">
+        <v>0.19622650426852628</v>
+      </c>
+      <c r="M52" s="8">
         <f t="shared" si="12"/>
-        <v>0.9811325213426314</v>
-      </c>
-      <c r="L52" s="5">
-        <f t="shared" si="13"/>
-        <v>0.19622650426852628</v>
-      </c>
-      <c r="M52" s="8">
-        <f t="shared" si="14"/>
         <v>0.7585344238137296</v>
       </c>
       <c r="N52" s="8">
@@ -6064,15 +6064,15 @@
         <v>-1.0550599111121368</v>
       </c>
       <c r="Q52" s="2">
+        <f t="shared" si="13"/>
+        <v>109.79296928184861</v>
+      </c>
+      <c r="R52" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.20703071815139668</v>
+      </c>
+      <c r="S52" s="9">
         <f t="shared" si="15"/>
-        <v>109.79296928184861</v>
-      </c>
-      <c r="R52" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.20703071815139668</v>
-      </c>
-      <c r="S52" s="9">
-        <f t="shared" si="17"/>
         <v>109.58593856369721</v>
       </c>
       <c r="T52" s="9">
@@ -6112,7 +6112,7 @@
         <v>3.075753885152396</v>
       </c>
     </row>
-    <row r="53" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="53" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
         <v>110</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>2700</v>
       </c>
       <c r="C53" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D53" s="4">
@@ -6139,23 +6139,23 @@
         <v>1.3717914991090268</v>
       </c>
       <c r="I53" s="5">
+        <f t="shared" si="8"/>
+        <v>0.10087156311540381</v>
+      </c>
+      <c r="J53" s="5">
+        <f t="shared" si="9"/>
+        <v>0.33288545790939461</v>
+      </c>
+      <c r="K53" s="5">
         <f t="shared" si="10"/>
-        <v>0.10087156311540381</v>
-      </c>
-      <c r="J53" s="5">
+        <v>0.43375702102479841</v>
+      </c>
+      <c r="L53" s="5">
         <f t="shared" si="11"/>
-        <v>0.33288545790939461</v>
-      </c>
-      <c r="K53" s="5">
+        <v>8.6751404204959692E-2</v>
+      </c>
+      <c r="M53" s="8">
         <f t="shared" si="12"/>
-        <v>0.43375702102479841</v>
-      </c>
-      <c r="L53" s="5">
-        <f t="shared" si="13"/>
-        <v>8.6751404204959692E-2</v>
-      </c>
-      <c r="M53" s="8">
-        <f t="shared" si="14"/>
         <v>0.32459431487611068</v>
       </c>
       <c r="N53" s="8">
@@ -6171,15 +6171,15 @@
         <v>0.20047315007354283</v>
       </c>
       <c r="Q53" s="2">
+        <f t="shared" si="13"/>
+        <v>110.01739132727427</v>
+      </c>
+      <c r="R53" s="9">
+        <f t="shared" si="14"/>
+        <v>1.7391327274271458E-2</v>
+      </c>
+      <c r="S53" s="9">
         <f t="shared" si="15"/>
-        <v>110.01739132727427</v>
-      </c>
-      <c r="R53" s="9">
-        <f t="shared" si="16"/>
-        <v>1.7391327274271458E-2</v>
-      </c>
-      <c r="S53" s="9">
-        <f t="shared" si="17"/>
         <v>110.03478265454854</v>
       </c>
       <c r="T53" s="9">
@@ -6219,7 +6219,7 @@
         <v>4.2395253502089467</v>
       </c>
     </row>
-    <row r="54" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="54" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A54" s="2">
         <v>110</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>2700</v>
       </c>
       <c r="C54" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D54" s="4">
@@ -6246,23 +6246,23 @@
         <v>1.4202357982466478</v>
       </c>
       <c r="I54" s="5">
+        <f t="shared" si="8"/>
+        <v>8.8773804521718749E-2</v>
+      </c>
+      <c r="J54" s="5">
+        <f t="shared" si="9"/>
+        <v>0.65782933477307226</v>
+      </c>
+      <c r="K54" s="5">
         <f t="shared" si="10"/>
-        <v>8.8773804521718749E-2</v>
-      </c>
-      <c r="J54" s="5">
+        <v>0.74660313929479105</v>
+      </c>
+      <c r="L54" s="5">
         <f t="shared" si="11"/>
-        <v>0.65782933477307226</v>
-      </c>
-      <c r="K54" s="5">
+        <v>0.14932062785895822</v>
+      </c>
+      <c r="M54" s="8">
         <f t="shared" si="12"/>
-        <v>0.74660313929479105</v>
-      </c>
-      <c r="L54" s="5">
-        <f t="shared" si="13"/>
-        <v>0.14932062785895822</v>
-      </c>
-      <c r="M54" s="8">
-        <f t="shared" si="14"/>
         <v>0.81207697843510185</v>
       </c>
       <c r="N54" s="8">
@@ -6278,15 +6278,15 @@
         <v>-0.83818194817398262</v>
       </c>
       <c r="Q54" s="2">
+        <f t="shared" si="13"/>
+        <v>109.87484214523862</v>
+      </c>
+      <c r="R54" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.12515785476138386</v>
+      </c>
+      <c r="S54" s="9">
         <f t="shared" si="15"/>
-        <v>109.87484214523862</v>
-      </c>
-      <c r="R54" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.12515785476138386</v>
-      </c>
-      <c r="S54" s="9">
-        <f t="shared" si="17"/>
         <v>109.74968429047723</v>
       </c>
       <c r="T54" s="9">
@@ -6326,7 +6326,7 @@
         <v>5.7240599977831668</v>
       </c>
     </row>
-    <row r="55" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="55" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A55" s="2">
         <v>110</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>2700</v>
       </c>
       <c r="C55" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D55" s="4">
@@ -6353,23 +6353,23 @@
         <v>1.1555210141357832</v>
       </c>
       <c r="I55" s="5">
+        <f t="shared" si="8"/>
+        <v>0.15468045495903682</v>
+      </c>
+      <c r="J55" s="5">
+        <f t="shared" si="9"/>
+        <v>0.57738847082429234</v>
+      </c>
+      <c r="K55" s="5">
         <f t="shared" si="10"/>
-        <v>0.15468045495903682</v>
-      </c>
-      <c r="J55" s="5">
+        <v>0.73206892578332916</v>
+      </c>
+      <c r="L55" s="5">
         <f t="shared" si="11"/>
-        <v>0.57738847082429234</v>
-      </c>
-      <c r="K55" s="5">
+        <v>0.14641378515666584</v>
+      </c>
+      <c r="M55" s="8">
         <f t="shared" si="12"/>
-        <v>0.73206892578332916</v>
-      </c>
-      <c r="L55" s="5">
-        <f t="shared" si="13"/>
-        <v>0.14641378515666584</v>
-      </c>
-      <c r="M55" s="8">
-        <f t="shared" si="14"/>
         <v>0.61632890882011004</v>
       </c>
       <c r="N55" s="8">
@@ -6385,15 +6385,15 @@
         <v>-1.0478849743173939</v>
       </c>
       <c r="Q55" s="2">
+        <f t="shared" si="13"/>
+        <v>109.8465751945014</v>
+      </c>
+      <c r="R55" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.15342480549860521</v>
+      </c>
+      <c r="S55" s="9">
         <f t="shared" si="15"/>
-        <v>109.8465751945014</v>
-      </c>
-      <c r="R55" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.15342480549860521</v>
-      </c>
-      <c r="S55" s="9">
-        <f t="shared" si="17"/>
         <v>109.6931503890028</v>
       </c>
       <c r="T55" s="9">
@@ -6433,7 +6433,7 @@
         <v>1.6327077824938312</v>
       </c>
     </row>
-    <row r="56" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="56" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="2">
         <v>110</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>2700</v>
       </c>
       <c r="C56" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D56" s="4">
@@ -6460,23 +6460,23 @@
         <v>1.8211681944531508</v>
       </c>
       <c r="I56" s="5">
+        <f t="shared" si="8"/>
+        <v>5.6103258164574669E-2</v>
+      </c>
+      <c r="J56" s="5">
+        <f t="shared" si="9"/>
+        <v>9.9646631216571482E-2</v>
+      </c>
+      <c r="K56" s="5">
         <f t="shared" si="10"/>
-        <v>5.6103258164574669E-2</v>
-      </c>
-      <c r="J56" s="5">
+        <v>0.15574988938114614</v>
+      </c>
+      <c r="L56" s="5">
         <f t="shared" si="11"/>
-        <v>9.9646631216571482E-2</v>
-      </c>
-      <c r="K56" s="5">
+        <v>3.114997787622923E-2</v>
+      </c>
+      <c r="M56" s="8">
         <f t="shared" si="12"/>
-        <v>0.15574988938114614</v>
-      </c>
-      <c r="L56" s="5">
-        <f t="shared" si="13"/>
-        <v>3.114997787622923E-2</v>
-      </c>
-      <c r="M56" s="8">
-        <f t="shared" si="14"/>
         <v>0.51934002611875285</v>
       </c>
       <c r="N56" s="8">
@@ -6492,15 +6492,15 @@
         <v>-0.64209843509170783</v>
       </c>
       <c r="Q56" s="2">
+        <f t="shared" si="13"/>
+        <v>109.97999864795253</v>
+      </c>
+      <c r="R56" s="9">
+        <f t="shared" si="14"/>
+        <v>-2.0001352047468109E-2</v>
+      </c>
+      <c r="S56" s="9">
         <f t="shared" si="15"/>
-        <v>109.97999864795253</v>
-      </c>
-      <c r="R56" s="9">
-        <f t="shared" si="16"/>
-        <v>-2.0001352047468109E-2</v>
-      </c>
-      <c r="S56" s="9">
-        <f t="shared" si="17"/>
         <v>109.95999729590505</v>
       </c>
       <c r="T56" s="9">
@@ -6540,7 +6540,7 @@
         <v>1.5749159331673592</v>
       </c>
     </row>
-    <row r="57" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="57" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="2">
         <v>110</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>2700</v>
       </c>
       <c r="C57" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D57" s="4">
@@ -6567,23 +6567,23 @@
         <v>0.82315821109448917</v>
       </c>
       <c r="I57" s="5">
+        <f t="shared" si="8"/>
+        <v>8.2088385044429404E-2</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" si="9"/>
+        <v>0.26221750718707509</v>
+      </c>
+      <c r="K57" s="5">
         <f t="shared" si="10"/>
-        <v>8.2088385044429404E-2</v>
-      </c>
-      <c r="J57" s="5">
+        <v>0.34430589223150448</v>
+      </c>
+      <c r="L57" s="5">
         <f t="shared" si="11"/>
-        <v>0.26221750718707509</v>
-      </c>
-      <c r="K57" s="5">
+        <v>6.8861178446300894E-2</v>
+      </c>
+      <c r="M57" s="8">
         <f t="shared" si="12"/>
-        <v>0.34430589223150448</v>
-      </c>
-      <c r="L57" s="5">
-        <f t="shared" si="13"/>
-        <v>6.8861178446300894E-2</v>
-      </c>
-      <c r="M57" s="8">
-        <f t="shared" si="14"/>
         <v>0.58305411751658809</v>
       </c>
       <c r="N57" s="8">
@@ -6599,15 +6599,15 @@
         <v>-1.2582891200970248</v>
       </c>
       <c r="Q57" s="2">
+        <f t="shared" si="13"/>
+        <v>109.91335272836396</v>
+      </c>
+      <c r="R57" s="9">
+        <f t="shared" si="14"/>
+        <v>-8.6647271636040163E-2</v>
+      </c>
+      <c r="S57" s="9">
         <f t="shared" si="15"/>
-        <v>109.91335272836396</v>
-      </c>
-      <c r="R57" s="9">
-        <f t="shared" si="16"/>
-        <v>-8.6647271636040163E-2</v>
-      </c>
-      <c r="S57" s="9">
-        <f t="shared" si="17"/>
         <v>109.82670545672792</v>
       </c>
       <c r="T57" s="9">
@@ -6647,7 +6647,7 @@
         <v>1.4452185496690504</v>
       </c>
     </row>
-    <row r="58" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="58" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A58" s="2">
         <v>110</v>
       </c>
@@ -6655,7 +6655,7 @@
         <v>2700</v>
       </c>
       <c r="C58" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D58" s="4">
@@ -6674,23 +6674,23 @@
         <v>1.8047375045466949</v>
       </c>
       <c r="I58" s="5">
+        <f t="shared" si="8"/>
+        <v>6.3390604582619331E-2</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="9"/>
+        <v>0.31111286123854087</v>
+      </c>
+      <c r="K58" s="5">
         <f t="shared" si="10"/>
-        <v>6.3390604582619331E-2</v>
-      </c>
-      <c r="J58" s="5">
+        <v>0.37450346582116023</v>
+      </c>
+      <c r="L58" s="5">
         <f t="shared" si="11"/>
-        <v>0.31111286123854087</v>
-      </c>
-      <c r="K58" s="5">
+        <v>7.4900693164232049E-2</v>
+      </c>
+      <c r="M58" s="8">
         <f t="shared" si="12"/>
-        <v>0.37450346582116023</v>
-      </c>
-      <c r="L58" s="5">
-        <f t="shared" si="13"/>
-        <v>7.4900693164232049E-2</v>
-      </c>
-      <c r="M58" s="8">
-        <f t="shared" si="14"/>
         <v>0.9199301516404812</v>
       </c>
       <c r="N58" s="8">
@@ -6706,15 +6706,15 @@
         <v>-1.0948808606232381</v>
       </c>
       <c r="Q58" s="2">
+        <f t="shared" si="13"/>
+        <v>109.91799266460706</v>
+      </c>
+      <c r="R58" s="9">
+        <f t="shared" si="14"/>
+        <v>-8.2007335392931466E-2</v>
+      </c>
+      <c r="S58" s="9">
         <f t="shared" si="15"/>
-        <v>109.91799266460706</v>
-      </c>
-      <c r="R58" s="9">
-        <f t="shared" si="16"/>
-        <v>-8.2007335392931466E-2</v>
-      </c>
-      <c r="S58" s="9">
-        <f t="shared" si="17"/>
         <v>109.83598532921413</v>
       </c>
       <c r="T58" s="9">
@@ -6754,7 +6754,7 @@
         <v>8.4974457302168318</v>
       </c>
     </row>
-    <row r="59" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="59" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A59" s="2">
         <v>110</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>2700</v>
       </c>
       <c r="C59" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D59" s="4">
@@ -6781,23 +6781,23 @@
         <v>1.8448457334238735</v>
       </c>
       <c r="I59" s="5">
+        <f t="shared" si="8"/>
+        <v>8.8397256078099895E-2</v>
+      </c>
+      <c r="J59" s="5">
+        <f t="shared" si="9"/>
+        <v>0.34374607570730181</v>
+      </c>
+      <c r="K59" s="5">
         <f t="shared" si="10"/>
-        <v>8.8397256078099895E-2</v>
-      </c>
-      <c r="J59" s="5">
+        <v>0.43214333178540171</v>
+      </c>
+      <c r="L59" s="5">
         <f t="shared" si="11"/>
-        <v>0.34374607570730181</v>
-      </c>
-      <c r="K59" s="5">
+        <v>8.6428666357080353E-2</v>
+      </c>
+      <c r="M59" s="8">
         <f t="shared" si="12"/>
-        <v>0.43214333178540171</v>
-      </c>
-      <c r="L59" s="5">
-        <f t="shared" si="13"/>
-        <v>8.6428666357080353E-2</v>
-      </c>
-      <c r="M59" s="8">
-        <f t="shared" si="14"/>
         <v>0.68881232328799924</v>
       </c>
       <c r="N59" s="8">
@@ -6813,15 +6813,15 @@
         <v>-0.94735772974932286</v>
       </c>
       <c r="Q59" s="2">
+        <f t="shared" si="13"/>
+        <v>109.91812113485469</v>
+      </c>
+      <c r="R59" s="9">
+        <f t="shared" si="14"/>
+        <v>-8.1878865145305318E-2</v>
+      </c>
+      <c r="S59" s="9">
         <f t="shared" si="15"/>
-        <v>109.91812113485469</v>
-      </c>
-      <c r="R59" s="9">
-        <f t="shared" si="16"/>
-        <v>-8.1878865145305318E-2</v>
-      </c>
-      <c r="S59" s="9">
-        <f t="shared" si="17"/>
         <v>109.83624226970939</v>
       </c>
       <c r="T59" s="9">
@@ -6861,7 +6861,7 @@
         <v>1.726182305968138</v>
       </c>
     </row>
-    <row r="60" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="60" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A60" s="2">
         <v>110</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>2700</v>
       </c>
       <c r="C60" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D60" s="4">
@@ -6888,23 +6888,23 @@
         <v>2.0912825732499929</v>
       </c>
       <c r="I60" s="5">
+        <f t="shared" si="8"/>
+        <v>0.10565666776022514</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="9"/>
+        <v>0.68233185565588406</v>
+      </c>
+      <c r="K60" s="5">
         <f t="shared" si="10"/>
-        <v>0.10565666776022514</v>
-      </c>
-      <c r="J60" s="5">
+        <v>0.78798852341610925</v>
+      </c>
+      <c r="L60" s="5">
         <f t="shared" si="11"/>
-        <v>0.68233185565588406</v>
-      </c>
-      <c r="K60" s="5">
+        <v>0.15759770468322187</v>
+      </c>
+      <c r="M60" s="8">
         <f t="shared" si="12"/>
-        <v>0.78798852341610925</v>
-      </c>
-      <c r="L60" s="5">
-        <f t="shared" si="13"/>
-        <v>0.15759770468322187</v>
-      </c>
-      <c r="M60" s="8">
-        <f t="shared" si="14"/>
         <v>0.71395508393280049</v>
       </c>
       <c r="N60" s="8">
@@ -6920,15 +6920,15 @@
         <v>-0.66037422276627844</v>
       </c>
       <c r="Q60" s="2">
+        <f t="shared" si="13"/>
+        <v>109.89592653826007</v>
+      </c>
+      <c r="R60" s="9">
+        <f t="shared" si="14"/>
+        <v>-0.10407346173993212</v>
+      </c>
+      <c r="S60" s="9">
         <f t="shared" si="15"/>
-        <v>109.89592653826007</v>
-      </c>
-      <c r="R60" s="9">
-        <f t="shared" si="16"/>
-        <v>-0.10407346173993212</v>
-      </c>
-      <c r="S60" s="9">
-        <f t="shared" si="17"/>
         <v>109.79185307652014</v>
       </c>
       <c r="T60" s="9">
@@ -6968,7 +6968,7 @@
         <v>3.6240246286816502</v>
       </c>
     </row>
-    <row r="61" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="61" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A61" s="2">
         <v>110</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>2700</v>
       </c>
       <c r="C61" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D61" s="4">
@@ -6995,23 +6995,23 @@
         <v>1.5648411120749091</v>
       </c>
       <c r="I61" s="5">
+        <f t="shared" si="8"/>
+        <v>0.13992695228170493</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="9"/>
+        <v>0.34241326956448603</v>
+      </c>
+      <c r="K61" s="5">
         <f t="shared" si="10"/>
-        <v>0.13992695228170493</v>
-      </c>
-      <c r="J61" s="5">
+        <v>0.48234022184619096</v>
+      </c>
+      <c r="L61" s="5">
         <f t="shared" si="11"/>
-        <v>0.34241326956448603</v>
-      </c>
-      <c r="K61" s="5">
+        <v>9.6468044369238198E-2</v>
+      </c>
+      <c r="M61" s="8">
         <f t="shared" si="12"/>
-        <v>0.48234022184619096</v>
-      </c>
-      <c r="L61" s="5">
-        <f t="shared" si="13"/>
-        <v>9.6468044369238198E-2</v>
-      </c>
-      <c r="M61" s="8">
-        <f t="shared" si="14"/>
         <v>0.63753000495463708</v>
       </c>
       <c r="N61" s="8">
@@ -7027,15 +7027,15 @@
         <v>-0.76293313148059538</v>
       </c>
       <c r="Q61" s="2">
+        <f t="shared" si="13"/>
+        <v>109.92640133282157</v>
+      </c>
+      <c r="R61" s="9">
+        <f t="shared" si="14"/>
+        <v>-7.3598667178431915E-2</v>
+      </c>
+      <c r="S61" s="9">
         <f t="shared" si="15"/>
-        <v>109.92640133282157</v>
-      </c>
-      <c r="R61" s="9">
-        <f t="shared" si="16"/>
-        <v>-7.3598667178431915E-2</v>
-      </c>
-      <c r="S61" s="9">
-        <f t="shared" si="17"/>
         <v>109.85280266564314</v>
       </c>
       <c r="T61" s="9">
@@ -7075,7 +7075,7 @@
         <v>2.2776331906198415</v>
       </c>
     </row>
-    <row r="62" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="62" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A62" s="2">
         <v>110</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>2700</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D62" s="4">
@@ -7102,23 +7102,23 @@
         <v>1.9706034004591702</v>
       </c>
       <c r="I62" s="5">
+        <f t="shared" si="8"/>
+        <v>7.4019306990173894E-2</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" si="9"/>
+        <v>0.20779467745214161</v>
+      </c>
+      <c r="K62" s="5">
         <f t="shared" si="10"/>
-        <v>7.4019306990173894E-2</v>
-      </c>
-      <c r="J62" s="5">
+        <v>0.28181398444231553</v>
+      </c>
+      <c r="L62" s="5">
         <f t="shared" si="11"/>
-        <v>0.20779467745214161</v>
-      </c>
-      <c r="K62" s="5">
+        <v>5.6362796888463108E-2</v>
+      </c>
+      <c r="M62" s="8">
         <f t="shared" si="12"/>
-        <v>0.28181398444231553</v>
-      </c>
-      <c r="L62" s="5">
-        <f t="shared" si="13"/>
-        <v>5.6362796888463108E-2</v>
-      </c>
-      <c r="M62" s="8">
-        <f t="shared" si="14"/>
         <v>0.7154627872589473</v>
       </c>
       <c r="N62" s="8">
@@ -7134,15 +7134,15 @@
         <v>-0.90249141646236886</v>
       </c>
       <c r="Q62" s="2">
+        <f t="shared" si="13"/>
+        <v>109.94913305960034</v>
+      </c>
+      <c r="R62" s="9">
+        <f t="shared" si="14"/>
+        <v>-5.0866940399649868E-2</v>
+      </c>
+      <c r="S62" s="9">
         <f t="shared" si="15"/>
-        <v>109.94913305960034</v>
-      </c>
-      <c r="R62" s="9">
-        <f t="shared" si="16"/>
-        <v>-5.0866940399649868E-2</v>
-      </c>
-      <c r="S62" s="9">
-        <f t="shared" si="17"/>
         <v>109.8982661192007</v>
       </c>
       <c r="T62" s="9">
@@ -7182,7 +7182,7 @@
         <v>3.5083703858570137</v>
       </c>
     </row>
-    <row r="63" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="63" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A63" s="2">
         <v>110</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>2700</v>
       </c>
       <c r="C63" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D63" s="4">
@@ -7209,23 +7209,23 @@
         <v>0.3325881709928265</v>
       </c>
       <c r="I63" s="5">
+        <f t="shared" si="8"/>
+        <v>4.3970064775186335E-2</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" si="9"/>
+        <v>0.1491535925714961</v>
+      </c>
+      <c r="K63" s="5">
         <f t="shared" si="10"/>
-        <v>4.3970064775186335E-2</v>
-      </c>
-      <c r="J63" s="5">
+        <v>0.19312365734668244</v>
+      </c>
+      <c r="L63" s="5">
         <f t="shared" si="11"/>
-        <v>0.1491535925714961</v>
-      </c>
-      <c r="K63" s="5">
+        <v>3.8624731469336489E-2</v>
+      </c>
+      <c r="M63" s="8">
         <f t="shared" si="12"/>
-        <v>0.19312365734668244</v>
-      </c>
-      <c r="L63" s="5">
-        <f t="shared" si="13"/>
-        <v>3.8624731469336489E-2</v>
-      </c>
-      <c r="M63" s="8">
-        <f t="shared" si="14"/>
         <v>0.4023516259283535</v>
       </c>
       <c r="N63" s="8">
@@ -7241,15 +7241,15 @@
         <v>-1.0440913100999387</v>
       </c>
       <c r="Q63" s="2">
+        <f t="shared" si="13"/>
+        <v>109.95967225351792</v>
+      </c>
+      <c r="R63" s="9">
+        <f t="shared" si="14"/>
+        <v>-4.0327746482077868E-2</v>
+      </c>
+      <c r="S63" s="9">
         <f t="shared" si="15"/>
-        <v>109.95967225351792</v>
-      </c>
-      <c r="R63" s="9">
-        <f t="shared" si="16"/>
-        <v>-4.0327746482077868E-2</v>
-      </c>
-      <c r="S63" s="9">
-        <f t="shared" si="17"/>
         <v>109.91934450703585</v>
       </c>
       <c r="T63" s="9">
@@ -7289,7 +7289,7 @@
         <v>2.0536902931710292</v>
       </c>
     </row>
-    <row r="64" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="64" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A64" s="2">
         <v>110</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>2700</v>
       </c>
       <c r="C64" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D64" s="4">
@@ -7316,23 +7316,23 @@
         <v>1.9530165410854059</v>
       </c>
       <c r="I64" s="5">
+        <f t="shared" si="8"/>
+        <v>5.3721638699645871E-2</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="9"/>
+        <v>0.40600324068399801</v>
+      </c>
+      <c r="K64" s="5">
         <f t="shared" si="10"/>
-        <v>5.3721638699645871E-2</v>
-      </c>
-      <c r="J64" s="5">
+        <v>0.45972487938364387</v>
+      </c>
+      <c r="L64" s="5">
         <f t="shared" si="11"/>
-        <v>0.40600324068399801</v>
-      </c>
-      <c r="K64" s="5">
+        <v>9.1944975876728785E-2</v>
+      </c>
+      <c r="M64" s="8">
         <f t="shared" si="12"/>
-        <v>0.45972487938364387</v>
-      </c>
-      <c r="L64" s="5">
-        <f t="shared" si="13"/>
-        <v>9.1944975876728785E-2</v>
-      </c>
-      <c r="M64" s="8">
-        <f t="shared" si="14"/>
         <v>0.84643494649896012</v>
       </c>
       <c r="N64" s="8">
@@ -7348,15 +7348,15 @@
         <v>-0.75143595882190783</v>
       </c>
       <c r="Q64" s="2">
+        <f t="shared" si="13"/>
+        <v>109.93090923889322</v>
+      </c>
+      <c r="R64" s="9">
+        <f t="shared" si="14"/>
+        <v>-6.9090761106786885E-2</v>
+      </c>
+      <c r="S64" s="9">
         <f t="shared" si="15"/>
-        <v>109.93090923889322</v>
-      </c>
-      <c r="R64" s="9">
-        <f t="shared" si="16"/>
-        <v>-6.9090761106786885E-2</v>
-      </c>
-      <c r="S64" s="9">
-        <f t="shared" si="17"/>
         <v>109.86181847778643</v>
       </c>
       <c r="T64" s="9">
@@ -7396,7 +7396,7 @@
         <v>4.5028029951802093</v>
       </c>
     </row>
-    <row r="65" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="65" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A65" s="2">
         <v>110</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>2700</v>
       </c>
       <c r="C65" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D65" s="4">
@@ -7423,23 +7423,23 @@
         <v>1.1701672692157228</v>
       </c>
       <c r="I65" s="5">
+        <f t="shared" si="8"/>
+        <v>6.1300079226810543E-2</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="9"/>
+        <v>0.31277062292377539</v>
+      </c>
+      <c r="K65" s="5">
         <f t="shared" si="10"/>
-        <v>6.1300079226810543E-2</v>
-      </c>
-      <c r="J65" s="5">
+        <v>0.37407070215058591</v>
+      </c>
+      <c r="L65" s="5">
         <f t="shared" si="11"/>
-        <v>0.31277062292377539</v>
-      </c>
-      <c r="K65" s="5">
+        <v>7.4814140430117179E-2</v>
+      </c>
+      <c r="M65" s="8">
         <f t="shared" si="12"/>
-        <v>0.37407070215058591</v>
-      </c>
-      <c r="L65" s="5">
-        <f t="shared" si="13"/>
-        <v>7.4814140430117179E-2</v>
-      </c>
-      <c r="M65" s="8">
-        <f t="shared" si="14"/>
         <v>0.42471261041023417</v>
       </c>
       <c r="N65" s="8">
@@ -7455,15 +7455,15 @@
         <v>-0.57349169897027685</v>
       </c>
       <c r="Q65" s="2">
+        <f t="shared" si="13"/>
+        <v>109.95709471149773</v>
+      </c>
+      <c r="R65" s="9">
+        <f t="shared" si="14"/>
+        <v>-4.2905288502268782E-2</v>
+      </c>
+      <c r="S65" s="9">
         <f t="shared" si="15"/>
-        <v>109.95709471149773</v>
-      </c>
-      <c r="R65" s="9">
-        <f t="shared" si="16"/>
-        <v>-4.2905288502268782E-2</v>
-      </c>
-      <c r="S65" s="9">
-        <f t="shared" si="17"/>
         <v>109.91418942299546</v>
       </c>
       <c r="T65" s="9">
@@ -7503,7 +7503,7 @@
         <v>3.1892354846413413</v>
       </c>
     </row>
-    <row r="66" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="66" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A66" s="2">
         <v>110</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>2700</v>
       </c>
       <c r="C66" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1415926535897927</v>
       </c>
       <c r="D66" s="4">
@@ -7530,23 +7530,23 @@
         <v>0.73248215361822522</v>
       </c>
       <c r="I66" s="5">
+        <f t="shared" si="8"/>
+        <v>3.6786536716413062E-2</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="9"/>
+        <v>0.16721650917759298</v>
+      </c>
+      <c r="K66" s="5">
         <f t="shared" si="10"/>
-        <v>3.6786536716413062E-2</v>
-      </c>
-      <c r="J66" s="5">
+        <v>0.20400304589400603</v>
+      </c>
+      <c r="L66" s="5">
         <f t="shared" si="11"/>
-        <v>0.16721650917759298</v>
-      </c>
-      <c r="K66" s="5">
+        <v>4.0800609178801212E-2</v>
+      </c>
+      <c r="M66" s="8">
         <f t="shared" si="12"/>
-        <v>0.20400304589400603</v>
-      </c>
-      <c r="L66" s="5">
-        <f t="shared" si="13"/>
-        <v>4.0800609178801212E-2</v>
-      </c>
-      <c r="M66" s="8">
-        <f t="shared" si="14"/>
         <v>0.52108770865751841</v>
       </c>
       <c r="N66" s="8">
@@ -7562,15 +7562,15 @@
         <v>-0.8738274946460034</v>
       </c>
       <c r="Q66" s="2">
+        <f t="shared" si="13"/>
+        <v>109.96434730590126</v>
+      </c>
+      <c r="R66" s="9">
+        <f t="shared" si="14"/>
+        <v>-3.5652694098742596E-2</v>
+      </c>
+      <c r="S66" s="9">
         <f t="shared" si="15"/>
-        <v>109.96434730590126</v>
-      </c>
-      <c r="R66" s="9">
-        <f t="shared" si="16"/>
-        <v>-3.5652694098742596E-2</v>
-      </c>
-      <c r="S66" s="9">
-        <f t="shared" si="17"/>
         <v>109.92869461180251</v>
       </c>
       <c r="T66" s="9">
@@ -7610,7 +7610,7 @@
         <v>2.8100025012619914</v>
       </c>
     </row>
-    <row r="67" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="67" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A67" s="2">
         <v>110</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>6.9609440761114545</v>
       </c>
     </row>
-    <row r="68" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="68" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A68" s="2">
         <v>110</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>4.7866894653065293</v>
       </c>
     </row>
-    <row r="69" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="69" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
         <v>110</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>1.6758241375011416</v>
       </c>
     </row>
-    <row r="70" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="70" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
         <v>110</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>1.5659234961871977</v>
       </c>
     </row>
-    <row r="71" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="71" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A71" s="2">
         <v>110</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>2.1475304503145791</v>
       </c>
     </row>
-    <row r="72" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="72" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A72" s="2">
         <v>110</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>2.4196204120521982</v>
       </c>
     </row>
-    <row r="73" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="73" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A73" s="2">
         <v>110</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>4.1076747276330385</v>
       </c>
     </row>
-    <row r="74" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="74" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A74" s="2">
         <v>110</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>1.7897546437464249</v>
       </c>
     </row>
-    <row r="75" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="75" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A75" s="2">
         <v>110</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>3.9868760839845776</v>
       </c>
     </row>
-    <row r="76" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="76" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A76" s="2">
         <v>110</v>
       </c>
@@ -8680,7 +8680,7 @@
         <v>13.498248578934044</v>
       </c>
     </row>
-    <row r="77" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="77" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A77" s="2">
         <v>110</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>4.0414580721088962</v>
       </c>
     </row>
-    <row r="78" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="78" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A78" s="2">
         <v>110</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>1.5121137350334735</v>
       </c>
     </row>
-    <row r="79" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="79" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A79" s="2">
         <v>110</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>2.2344766163326848</v>
       </c>
     </row>
-    <row r="80" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="80" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A80" s="2">
         <v>110</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>2.7939787303740053</v>
       </c>
     </row>
-    <row r="81" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="81" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
         <v>110</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>2.0247305784463614</v>
       </c>
     </row>
-    <row r="82" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="82" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A82" s="2">
         <v>110</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>1.9951068061485535</v>
       </c>
     </row>
-    <row r="83" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="83" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A83" s="2">
         <v>110</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>1.6016311865509492</v>
       </c>
     </row>
-    <row r="84" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="84" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A84" s="2">
         <v>110</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>4.9266434257095444</v>
       </c>
     </row>
-    <row r="85" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="85" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A85" s="2">
         <v>110</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>2.6189809252633895</v>
       </c>
     </row>
-    <row r="86" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="86" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A86" s="2">
         <v>110</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>7.9065334991505303</v>
       </c>
     </row>
-    <row r="87" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="87" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A87" s="2">
         <v>110</v>
       </c>
@@ -9857,7 +9857,7 @@
         <v>12.348574082741818</v>
       </c>
     </row>
-    <row r="88" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="88" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A88" s="2">
         <v>110</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>2.6602129394542939</v>
       </c>
     </row>
-    <row r="89" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="89" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A89" s="2">
         <v>110</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>2.0132384285655962</v>
       </c>
     </row>
-    <row r="90" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="90" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A90" s="2">
         <v>110</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>1.5475484266820509</v>
       </c>
     </row>
-    <row r="91" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="91" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A91" s="2">
         <v>110</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>3.2289706740320923</v>
       </c>
     </row>
-    <row r="92" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="92" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A92" s="2">
         <v>110</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>2.4668006808952683</v>
       </c>
     </row>
-    <row r="93" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="93" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A93" s="2">
         <v>110</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1.8699770788218359</v>
       </c>
     </row>
-    <row r="94" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="94" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A94" s="2">
         <v>110</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>1.8431648749822123</v>
       </c>
     </row>
-    <row r="95" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="95" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A95" s="2">
         <v>110</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>2.7037809964617092</v>
       </c>
     </row>
-    <row r="96" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="96" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A96" s="2">
         <v>110</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>3.6508294268024688</v>
       </c>
     </row>
-    <row r="97" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="97" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A97" s="2">
         <v>110</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>3.2033870904421455</v>
       </c>
     </row>
-    <row r="98" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="98" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A98" s="2">
         <v>110</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>2.0569227174348428</v>
       </c>
     </row>
-    <row r="99" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="99" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A99" s="2">
         <v>110</v>
       </c>
@@ -11141,7 +11141,7 @@
         <v>3.3479431581484977</v>
       </c>
     </row>
-    <row r="100" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="100" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A100" s="2">
         <v>110</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>8.9524008580513676</v>
       </c>
     </row>
-    <row r="101" spans="1:28" s="2" customFormat="1" ht="14">
+    <row r="101" spans="1:28" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A101" s="2">
         <v>110</v>
       </c>
@@ -11355,10 +11355,10 @@
         <v>3.2449591916756164</v>
       </c>
     </row>
-    <row r="103" spans="1:28">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="Z103" s="2"/>
     </row>
-    <row r="111" spans="1:28">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
@@ -11376,1144 +11376,1144 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E5F16D-1ED6-EF4C-9EFB-F3F95EEB1154}">
   <dimension ref="B83:C366"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="83" spans="2:3">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
     </row>
-    <row r="84" spans="2:3">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
     </row>
-    <row r="85" spans="2:3">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
     </row>
-    <row r="86" spans="2:3">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
     </row>
-    <row r="87" spans="2:3">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
     </row>
-    <row r="88" spans="2:3">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
     </row>
-    <row r="89" spans="2:3">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
     </row>
-    <row r="90" spans="2:3">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
     </row>
-    <row r="91" spans="2:3">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
     </row>
-    <row r="92" spans="2:3">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="2:3">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
     </row>
-    <row r="94" spans="2:3">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="2:3">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
     </row>
-    <row r="96" spans="2:3">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
     </row>
-    <row r="97" spans="2:3">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
     </row>
-    <row r="98" spans="2:3">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
     </row>
-    <row r="99" spans="2:3">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="2:3">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="2:3">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="2:3">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" spans="2:3">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="2:3">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="2:3">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="2:3">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="2:3">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" spans="2:3">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="2:3">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" spans="2:3">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="2:3">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="2:3">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="2:3">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" spans="2:3">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" spans="2:3">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="2:3">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="2:3">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="2:3">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="2:3">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="2:3">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" spans="2:3">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="2:3">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="2:3">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="2:3">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="2:3">
+    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="2:3">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
     </row>
-    <row r="127" spans="2:3">
+    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="2:3">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="2:3">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
     </row>
-    <row r="130" spans="2:3">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
     </row>
-    <row r="131" spans="2:3">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
     </row>
-    <row r="132" spans="2:3">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="2:3">
+    <row r="133" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="2:3">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="2:3">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="2:3">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="2:3">
+    <row r="137" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
     </row>
-    <row r="138" spans="2:3">
+    <row r="138" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="2:3">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
     </row>
-    <row r="140" spans="2:3">
+    <row r="140" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="2:3">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="2:3">
+    <row r="142" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="2:3">
+    <row r="143" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
     </row>
-    <row r="144" spans="2:3">
+    <row r="144" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="2:3">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="2:3">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
     </row>
-    <row r="147" spans="2:3">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
     </row>
-    <row r="148" spans="2:3">
+    <row r="148" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="2:3">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="2:3">
+    <row r="150" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="2:3">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="2:3">
+    <row r="152" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
     </row>
-    <row r="153" spans="2:3">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
     </row>
-    <row r="154" spans="2:3">
+    <row r="154" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
     </row>
-    <row r="155" spans="2:3">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
     </row>
-    <row r="156" spans="2:3">
+    <row r="156" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="2:3">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="2:3">
+    <row r="158" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="2:3">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="2:3">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="2:3">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="2:3">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
     </row>
-    <row r="163" spans="2:3">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
     </row>
-    <row r="164" spans="2:3">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="2:3">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="2:3">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="2:3">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="2:3">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
     </row>
-    <row r="169" spans="2:3">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
     </row>
-    <row r="170" spans="2:3">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
     </row>
-    <row r="171" spans="2:3">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
     </row>
-    <row r="172" spans="2:3">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
     </row>
-    <row r="173" spans="2:3">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="2:3">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="2:3">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
     </row>
-    <row r="176" spans="2:3">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
     </row>
-    <row r="177" spans="2:3">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="2:3">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="2:3">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
     </row>
-    <row r="180" spans="2:3">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="2:3">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="2:3">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="2:3">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
     </row>
-    <row r="184" spans="2:3">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
     </row>
-    <row r="185" spans="2:3">
+    <row r="185" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
     </row>
-    <row r="186" spans="2:3">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
     </row>
-    <row r="187" spans="2:3">
+    <row r="187" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
     </row>
-    <row r="188" spans="2:3">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
     </row>
-    <row r="189" spans="2:3">
+    <row r="189" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
     </row>
-    <row r="190" spans="2:3">
+    <row r="190" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
     </row>
-    <row r="191" spans="2:3">
+    <row r="191" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
     </row>
-    <row r="192" spans="2:3">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
     </row>
-    <row r="193" spans="2:3">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
     </row>
-    <row r="194" spans="2:3">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
     </row>
-    <row r="195" spans="2:3">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
     </row>
-    <row r="196" spans="2:3">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
     </row>
-    <row r="197" spans="2:3">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
     </row>
-    <row r="198" spans="2:3">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
     </row>
-    <row r="199" spans="2:3">
+    <row r="199" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
     </row>
-    <row r="200" spans="2:3">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
     </row>
-    <row r="201" spans="2:3">
+    <row r="201" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
     </row>
-    <row r="202" spans="2:3">
+    <row r="202" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
     </row>
-    <row r="203" spans="2:3">
+    <row r="203" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
     </row>
-    <row r="204" spans="2:3">
+    <row r="204" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
     </row>
-    <row r="205" spans="2:3">
+    <row r="205" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
     </row>
-    <row r="206" spans="2:3">
+    <row r="206" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
     </row>
-    <row r="207" spans="2:3">
+    <row r="207" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
     </row>
-    <row r="208" spans="2:3">
+    <row r="208" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
     </row>
-    <row r="209" spans="2:3">
+    <row r="209" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
     </row>
-    <row r="210" spans="2:3">
+    <row r="210" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
     </row>
-    <row r="211" spans="2:3">
+    <row r="211" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
     </row>
-    <row r="212" spans="2:3">
+    <row r="212" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
     </row>
-    <row r="213" spans="2:3">
+    <row r="213" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
     </row>
-    <row r="214" spans="2:3">
+    <row r="214" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
     </row>
-    <row r="215" spans="2:3">
+    <row r="215" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
     </row>
-    <row r="216" spans="2:3">
+    <row r="216" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
     </row>
-    <row r="217" spans="2:3">
+    <row r="217" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
     </row>
-    <row r="218" spans="2:3">
+    <row r="218" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
     </row>
-    <row r="219" spans="2:3">
+    <row r="219" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
     </row>
-    <row r="220" spans="2:3">
+    <row r="220" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
     </row>
-    <row r="221" spans="2:3">
+    <row r="221" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
     </row>
-    <row r="222" spans="2:3">
+    <row r="222" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
     </row>
-    <row r="223" spans="2:3">
+    <row r="223" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
     </row>
-    <row r="224" spans="2:3">
+    <row r="224" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
     </row>
-    <row r="225" spans="2:3">
+    <row r="225" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
     </row>
-    <row r="226" spans="2:3">
+    <row r="226" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
     </row>
-    <row r="227" spans="2:3">
+    <row r="227" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
     </row>
-    <row r="228" spans="2:3">
+    <row r="228" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
     </row>
-    <row r="229" spans="2:3">
+    <row r="229" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
     </row>
-    <row r="230" spans="2:3">
+    <row r="230" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
     </row>
-    <row r="231" spans="2:3">
+    <row r="231" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
     </row>
-    <row r="232" spans="2:3">
+    <row r="232" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
     </row>
-    <row r="233" spans="2:3">
+    <row r="233" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
     </row>
-    <row r="234" spans="2:3">
+    <row r="234" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
     </row>
-    <row r="235" spans="2:3">
+    <row r="235" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
     </row>
-    <row r="236" spans="2:3">
+    <row r="236" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
     </row>
-    <row r="237" spans="2:3">
+    <row r="237" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
     </row>
-    <row r="238" spans="2:3">
+    <row r="238" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
     </row>
-    <row r="239" spans="2:3">
+    <row r="239" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
     </row>
-    <row r="240" spans="2:3">
+    <row r="240" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
     </row>
-    <row r="241" spans="2:3">
+    <row r="241" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
     </row>
-    <row r="242" spans="2:3">
+    <row r="242" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
     </row>
-    <row r="243" spans="2:3">
+    <row r="243" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
     </row>
-    <row r="244" spans="2:3">
+    <row r="244" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
     </row>
-    <row r="245" spans="2:3">
+    <row r="245" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
     </row>
-    <row r="246" spans="2:3">
+    <row r="246" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
     </row>
-    <row r="247" spans="2:3">
+    <row r="247" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
     </row>
-    <row r="248" spans="2:3">
+    <row r="248" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
     </row>
-    <row r="249" spans="2:3">
+    <row r="249" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
     </row>
-    <row r="250" spans="2:3">
+    <row r="250" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
     </row>
-    <row r="251" spans="2:3">
+    <row r="251" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
     </row>
-    <row r="252" spans="2:3">
+    <row r="252" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
     </row>
-    <row r="253" spans="2:3">
+    <row r="253" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
     </row>
-    <row r="254" spans="2:3">
+    <row r="254" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
     </row>
-    <row r="255" spans="2:3">
+    <row r="255" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
     </row>
-    <row r="256" spans="2:3">
+    <row r="256" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
     </row>
-    <row r="257" spans="2:3">
+    <row r="257" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
     </row>
-    <row r="258" spans="2:3">
+    <row r="258" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
     </row>
-    <row r="259" spans="2:3">
+    <row r="259" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
     </row>
-    <row r="260" spans="2:3">
+    <row r="260" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
     </row>
-    <row r="261" spans="2:3">
+    <row r="261" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
     </row>
-    <row r="262" spans="2:3">
+    <row r="262" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
     </row>
-    <row r="263" spans="2:3">
+    <row r="263" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
     </row>
-    <row r="264" spans="2:3">
+    <row r="264" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
     </row>
-    <row r="265" spans="2:3">
+    <row r="265" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
     </row>
-    <row r="266" spans="2:3">
+    <row r="266" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
     </row>
-    <row r="267" spans="2:3">
+    <row r="267" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
     </row>
-    <row r="268" spans="2:3">
+    <row r="268" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
     </row>
-    <row r="269" spans="2:3">
+    <row r="269" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
     </row>
-    <row r="270" spans="2:3">
+    <row r="270" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
     </row>
-    <row r="271" spans="2:3">
+    <row r="271" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
     </row>
-    <row r="272" spans="2:3">
+    <row r="272" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
     </row>
-    <row r="273" spans="2:3">
+    <row r="273" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
     </row>
-    <row r="274" spans="2:3">
+    <row r="274" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
     </row>
-    <row r="275" spans="2:3">
+    <row r="275" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
     </row>
-    <row r="276" spans="2:3">
+    <row r="276" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
     </row>
-    <row r="277" spans="2:3">
+    <row r="277" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="2:3">
+    <row r="278" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
     </row>
-    <row r="279" spans="2:3">
+    <row r="279" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
     </row>
-    <row r="280" spans="2:3">
+    <row r="280" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
     </row>
-    <row r="281" spans="2:3">
+    <row r="281" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
     </row>
-    <row r="282" spans="2:3">
+    <row r="282" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
     </row>
-    <row r="283" spans="2:3">
+    <row r="283" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
     </row>
-    <row r="284" spans="2:3">
+    <row r="284" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
     </row>
-    <row r="285" spans="2:3">
+    <row r="285" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
     </row>
-    <row r="286" spans="2:3">
+    <row r="286" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
     </row>
-    <row r="287" spans="2:3">
+    <row r="287" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
     </row>
-    <row r="288" spans="2:3">
+    <row r="288" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
     </row>
-    <row r="289" spans="2:3">
+    <row r="289" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
     </row>
-    <row r="290" spans="2:3">
+    <row r="290" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
     </row>
-    <row r="291" spans="2:3">
+    <row r="291" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
     </row>
-    <row r="292" spans="2:3">
+    <row r="292" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
     </row>
-    <row r="293" spans="2:3">
+    <row r="293" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
     </row>
-    <row r="294" spans="2:3">
+    <row r="294" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
     </row>
-    <row r="295" spans="2:3">
+    <row r="295" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
     </row>
-    <row r="296" spans="2:3">
+    <row r="296" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
     </row>
-    <row r="297" spans="2:3">
+    <row r="297" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
     </row>
-    <row r="298" spans="2:3">
+    <row r="298" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
     </row>
-    <row r="299" spans="2:3">
+    <row r="299" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
     </row>
-    <row r="300" spans="2:3">
+    <row r="300" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
     </row>
-    <row r="301" spans="2:3">
+    <row r="301" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
     </row>
-    <row r="302" spans="2:3">
+    <row r="302" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
     </row>
-    <row r="303" spans="2:3">
+    <row r="303" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
     </row>
-    <row r="304" spans="2:3">
+    <row r="304" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
     </row>
-    <row r="305" spans="2:3">
+    <row r="305" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
     </row>
-    <row r="306" spans="2:3">
+    <row r="306" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
     </row>
-    <row r="307" spans="2:3">
+    <row r="307" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
     </row>
-    <row r="308" spans="2:3">
+    <row r="308" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
     </row>
-    <row r="309" spans="2:3">
+    <row r="309" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
     </row>
-    <row r="310" spans="2:3">
+    <row r="310" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
     </row>
-    <row r="311" spans="2:3">
+    <row r="311" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
     </row>
-    <row r="312" spans="2:3">
+    <row r="312" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
     </row>
-    <row r="313" spans="2:3">
+    <row r="313" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
     </row>
-    <row r="314" spans="2:3">
+    <row r="314" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
     </row>
-    <row r="315" spans="2:3">
+    <row r="315" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
     </row>
-    <row r="316" spans="2:3">
+    <row r="316" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
     </row>
-    <row r="317" spans="2:3">
+    <row r="317" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
     </row>
-    <row r="318" spans="2:3">
+    <row r="318" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
     </row>
-    <row r="319" spans="2:3">
+    <row r="319" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
     </row>
-    <row r="320" spans="2:3">
+    <row r="320" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
     </row>
-    <row r="321" spans="2:3">
+    <row r="321" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
     </row>
-    <row r="322" spans="2:3">
+    <row r="322" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
     </row>
-    <row r="323" spans="2:3">
+    <row r="323" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
     </row>
-    <row r="324" spans="2:3">
+    <row r="324" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
     </row>
-    <row r="325" spans="2:3">
+    <row r="325" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
     </row>
-    <row r="326" spans="2:3">
+    <row r="326" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
     </row>
-    <row r="327" spans="2:3">
+    <row r="327" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
     </row>
-    <row r="328" spans="2:3">
+    <row r="328" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
     </row>
-    <row r="329" spans="2:3">
+    <row r="329" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
     </row>
-    <row r="330" spans="2:3">
+    <row r="330" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
     </row>
-    <row r="331" spans="2:3">
+    <row r="331" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
     </row>
-    <row r="332" spans="2:3">
+    <row r="332" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
     </row>
-    <row r="333" spans="2:3">
+    <row r="333" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
     </row>
-    <row r="334" spans="2:3">
+    <row r="334" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
     </row>
-    <row r="335" spans="2:3">
+    <row r="335" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
     </row>
-    <row r="336" spans="2:3">
+    <row r="336" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
     </row>
-    <row r="337" spans="2:3">
+    <row r="337" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
     </row>
-    <row r="338" spans="2:3">
+    <row r="338" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
     </row>
-    <row r="339" spans="2:3">
+    <row r="339" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
     </row>
-    <row r="340" spans="2:3">
+    <row r="340" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
     </row>
-    <row r="341" spans="2:3">
+    <row r="341" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
     </row>
-    <row r="342" spans="2:3">
+    <row r="342" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
     </row>
-    <row r="343" spans="2:3">
+    <row r="343" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
     </row>
-    <row r="344" spans="2:3">
+    <row r="344" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
     </row>
-    <row r="345" spans="2:3">
+    <row r="345" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
     </row>
-    <row r="346" spans="2:3">
+    <row r="346" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
     </row>
-    <row r="347" spans="2:3">
+    <row r="347" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
     </row>
-    <row r="348" spans="2:3">
+    <row r="348" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
     </row>
-    <row r="349" spans="2:3">
+    <row r="349" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
     </row>
-    <row r="350" spans="2:3">
+    <row r="350" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
     </row>
-    <row r="351" spans="2:3">
+    <row r="351" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
     </row>
-    <row r="352" spans="2:3">
+    <row r="352" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
     </row>
-    <row r="353" spans="2:3">
+    <row r="353" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
     </row>
-    <row r="354" spans="2:3">
+    <row r="354" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
     </row>
-    <row r="355" spans="2:3">
+    <row r="355" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
     </row>
-    <row r="356" spans="2:3">
+    <row r="356" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
     </row>
-    <row r="357" spans="2:3">
+    <row r="357" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
     </row>
-    <row r="358" spans="2:3">
+    <row r="358" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
     </row>
-    <row r="359" spans="2:3">
+    <row r="359" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
     </row>
-    <row r="360" spans="2:3">
+    <row r="360" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
     </row>
-    <row r="361" spans="2:3">
+    <row r="361" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
     </row>
-    <row r="362" spans="2:3">
+    <row r="362" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
     </row>
-    <row r="363" spans="2:3">
+    <row r="363" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
     </row>
-    <row r="364" spans="2:3">
+    <row r="364" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
     </row>
-    <row r="365" spans="2:3">
+    <row r="365" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
     </row>
-    <row r="366" spans="2:3">
+    <row r="366" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
     </row>
